--- a/assets/card_data.xlsx
+++ b/assets/card_data.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="6"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="人物" sheetId="1" state="visible" r:id="rId3"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="167">
   <si>
     <t xml:space="preserve">name</t>
   </si>
@@ -140,7 +140,7 @@
     <t xml:space="preserve">是否是遗物</t>
   </si>
   <si>
-    <t xml:space="preserve">生鱼</t>
+    <t xml:space="preserve">鱼</t>
   </si>
   <si>
     <t xml:space="preserve">食物</t>
@@ -149,7 +149,7 @@
     <t xml:space="preserve">res://assets/resources/fish</t>
   </si>
   <si>
-    <t xml:space="preserve">生肉</t>
+    <t xml:space="preserve">肉</t>
   </si>
   <si>
     <t xml:space="preserve">res://assets/resources/meat</t>
@@ -515,6 +515,12 @@
   </si>
   <si>
     <t xml:space="preserve">需要设定合成的时间</t>
+  </si>
+  <si>
+    <t xml:space="preserve">生鱼</t>
+  </si>
+  <si>
+    <t xml:space="preserve">生肉</t>
   </si>
   <si>
     <t xml:space="preserve">卡片类型信息表</t>
@@ -771,80 +777,76 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="18">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="justify" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="justify" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="justify" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1122,25 +1124,25 @@
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="0" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="0" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="0" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="0" t="s">
+      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="0" t="s">
+      <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="0" t="s">
+      <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="0" t="s">
+      <c r="L1" s="2" t="s">
         <v>11</v>
       </c>
       <c r="M1" s="1" t="s">
@@ -1150,7 +1152,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="55.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="77.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
         <v>14</v>
       </c>
@@ -1166,13 +1168,13 @@
       <c r="F2" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="G2" s="3" t="s">
         <v>16</v>
       </c>
       <c r="M2" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="T2" s="3" t="s">
+      <c r="T2" s="4" t="s">
         <v>18</v>
       </c>
     </row>
@@ -1192,7 +1194,7 @@
       <c r="M3" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="T3" s="3" t="s">
+      <c r="T3" s="4" t="s">
         <v>21</v>
       </c>
     </row>
@@ -1297,7 +1299,7 @@
       <c r="H2" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="I2" s="4" t="b">
+      <c r="I2" s="1" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
@@ -1324,7 +1326,7 @@
       <c r="H3" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="I3" s="4" t="b">
+      <c r="I3" s="1" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
@@ -1345,7 +1347,7 @@
       <c r="D4" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="E4" s="3" t="s">
         <v>41</v>
       </c>
       <c r="G4" s="1" t="n">
@@ -1354,7 +1356,7 @@
       <c r="H4" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="I4" s="4" t="b">
+      <c r="I4" s="1" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
@@ -1381,7 +1383,7 @@
       <c r="H5" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="I5" s="4" t="b">
+      <c r="I5" s="1" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
@@ -1390,7 +1392,7 @@
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="2" t="s">
+      <c r="A6" s="3" t="s">
         <v>44</v>
       </c>
       <c r="B6" s="1" t="s">
@@ -1408,7 +1410,7 @@
       <c r="H6" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="I6" s="4" t="b">
+      <c r="I6" s="1" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
@@ -1438,7 +1440,7 @@
       <c r="H7" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="I7" s="4" t="b">
+      <c r="I7" s="1" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
@@ -1468,7 +1470,7 @@
       <c r="H8" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="I8" s="4" t="b">
+      <c r="I8" s="1" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
@@ -1498,7 +1500,7 @@
       <c r="H9" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="I9" s="4" t="b">
+      <c r="I9" s="1" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
@@ -1528,7 +1530,7 @@
       <c r="H10" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="I10" s="4" t="b">
+      <c r="I10" s="1" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
@@ -1555,7 +1557,7 @@
       <c r="H11" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="I11" s="4" t="b">
+      <c r="I11" s="1" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
@@ -1576,14 +1578,14 @@
       <c r="D12" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="E12" s="2"/>
+      <c r="E12" s="3"/>
       <c r="G12" s="1" t="n">
         <v>11</v>
       </c>
       <c r="H12" s="1" t="n">
         <v>100</v>
       </c>
-      <c r="I12" s="4" t="b">
+      <c r="I12" s="1" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
@@ -1592,10 +1594,10 @@
       </c>
     </row>
     <row r="13" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="2" t="s">
+      <c r="A13" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="B13" s="3" t="s">
         <v>40</v>
       </c>
       <c r="C13" s="1" t="n">
@@ -1607,7 +1609,7 @@
       <c r="G13" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="H13" s="0" t="n">
+      <c r="H13" s="2" t="n">
         <v>20</v>
       </c>
       <c r="I13" s="5" t="b">
@@ -1639,7 +1641,7 @@
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="14.11"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="3" min="2" style="1" width="9.98"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="30.22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="2" width="30.22"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="7" min="6" style="1" width="9.98"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="6.64"/>
   </cols>
@@ -1654,10 +1656,10 @@
       <c r="C1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="D1" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="E1" s="0" t="s">
+      <c r="E1" s="2" t="s">
         <v>30</v>
       </c>
       <c r="F1" s="1" t="s">
@@ -1680,7 +1682,7 @@
       <c r="C2" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="D2" s="0" t="n">
+      <c r="D2" s="2" t="n">
         <v>13</v>
       </c>
       <c r="F2" s="1" t="n">
@@ -1703,7 +1705,7 @@
       <c r="C3" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="D3" s="0" t="n">
+      <c r="D3" s="2" t="n">
         <v>14</v>
       </c>
       <c r="F3" s="1" t="n">
@@ -1726,7 +1728,7 @@
       <c r="C4" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="D4" s="0" t="n">
+      <c r="D4" s="2" t="n">
         <v>15</v>
       </c>
       <c r="F4" s="1" t="n">
@@ -1749,10 +1751,10 @@
       <c r="C5" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="D5" s="0" t="n">
+      <c r="D5" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="E5" s="0" t="s">
+      <c r="E5" s="2" t="s">
         <v>67</v>
       </c>
       <c r="F5" s="1" t="n">
@@ -1775,10 +1777,10 @@
       <c r="C6" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="D6" s="0" t="n">
+      <c r="D6" s="2" t="n">
         <v>17</v>
       </c>
-      <c r="E6" s="0" t="s">
+      <c r="E6" s="2" t="s">
         <v>70</v>
       </c>
       <c r="F6" s="1" t="n">
@@ -1801,7 +1803,7 @@
       <c r="C7" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D7" s="0" t="n">
+      <c r="D7" s="2" t="n">
         <v>18</v>
       </c>
       <c r="F7" s="1" t="n">
@@ -1824,7 +1826,7 @@
       <c r="C8" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="D8" s="0" t="n">
+      <c r="D8" s="2" t="n">
         <v>20</v>
       </c>
       <c r="F8" s="1" t="n">
@@ -1847,7 +1849,7 @@
       <c r="C9" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="D9" s="0" t="n">
+      <c r="D9" s="2" t="n">
         <v>21</v>
       </c>
       <c r="E9" s="6" t="s">
@@ -1856,7 +1858,7 @@
       <c r="F9" s="1" t="n">
         <v>150</v>
       </c>
-      <c r="G9" s="4" t="b">
+      <c r="G9" s="1" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
@@ -1874,7 +1876,7 @@
       <c r="C10" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="D10" s="0" t="n">
+      <c r="D10" s="2" t="n">
         <v>22</v>
       </c>
       <c r="E10" s="6" t="s">
@@ -1900,7 +1902,7 @@
       <c r="C11" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="D11" s="0" t="n">
+      <c r="D11" s="2" t="n">
         <v>23</v>
       </c>
       <c r="E11" s="6" t="s">
@@ -1926,7 +1928,7 @@
       <c r="C12" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D12" s="0" t="n">
+      <c r="D12" s="2" t="n">
         <v>24</v>
       </c>
       <c r="E12" s="6" t="s">
@@ -1952,13 +1954,13 @@
       <c r="C13" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="D13" s="0" t="n">
+      <c r="D13" s="2" t="n">
         <v>25</v>
       </c>
       <c r="F13" s="1" t="n">
         <v>120</v>
       </c>
-      <c r="G13" s="4" t="b">
+      <c r="G13" s="1" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
@@ -2045,7 +2047,7 @@
       <c r="D3" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="E3" s="4" t="b">
+      <c r="E3" s="1" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
@@ -2089,7 +2091,7 @@
       <c r="D5" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="E5" s="4" t="b">
+      <c r="E5" s="1" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
@@ -2101,13 +2103,13 @@
       </c>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0"/>
-      <c r="B6" s="0"/>
-      <c r="C6" s="0"/>
-      <c r="D6" s="0"/>
-      <c r="E6" s="0"/>
-      <c r="F6" s="0"/>
-      <c r="G6" s="0"/>
+      <c r="A6" s="2"/>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+      <c r="F6" s="2"/>
+      <c r="G6" s="2"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -2281,80 +2283,80 @@
   <sheetFormatPr defaultColWidth="11.7265625" defaultRowHeight="13.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="D1" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="E1" s="0" t="s">
+      <c r="E1" s="2" t="s">
         <v>116</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="A2" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="C2" s="0" t="n">
+      <c r="C2" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="E2" s="0" t="s">
+      <c r="E2" s="2" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+      <c r="A3" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="B3" s="0" t="s">
+      <c r="B3" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="C3" s="0" t="n">
+      <c r="C3" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="D3" s="0" t="n">
+      <c r="D3" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E3" s="0" t="s">
+      <c r="E3" s="2" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+      <c r="A4" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="B4" s="0" t="s">
+      <c r="B4" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="C4" s="0" t="n">
+      <c r="C4" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="E4" s="0" t="s">
+      <c r="E4" s="2" t="s">
         <v>122</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+      <c r="A5" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="B5" s="0" t="s">
+      <c r="B5" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="C5" s="0" t="n">
+      <c r="C5" s="2" t="n">
         <v>1000</v>
       </c>
-      <c r="E5" s="0" t="s">
+      <c r="E5" s="2" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
+      <c r="A7" s="2" t="s">
         <v>125</v>
       </c>
     </row>
@@ -2377,7 +2379,7 @@
   <dimension ref="A1:C25"/>
   <sheetFormatPr defaultColWidth="9.00390625" defaultRowHeight="13.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="14.11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="2" width="14.11"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2387,13 +2389,13 @@
       <c r="B1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" s="2" t="s">
         <v>126</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="7" t="s">
-        <v>34</v>
+        <v>127</v>
       </c>
       <c r="B2" s="7" t="n">
         <v>1</v>
@@ -2401,7 +2403,7 @@
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="7" t="s">
-        <v>37</v>
+        <v>128</v>
       </c>
       <c r="B3" s="7" t="n">
         <v>2</v>
@@ -2602,18 +2604,18 @@
   <dimension ref="A1:G7"/>
   <sheetFormatPr defaultColWidth="9.00390625" defaultRowHeight="13.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="9.63"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="50.63"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="18.5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="28.25"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="49.63"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="50.63"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="2" width="9.63"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="50.63"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="2" width="18.5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="2" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="2" width="28.25"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="2" width="49.63"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="2" width="50.63"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="12" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B1" s="12"/>
       <c r="C1" s="12"/>
@@ -2624,145 +2626,145 @@
     </row>
     <row r="2" customFormat="false" ht="16.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="13" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="B2" s="14" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="C2" s="13" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="D2" s="13" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="E2" s="13" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="F2" s="13" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="G2" s="14" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="30.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="15" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="B3" s="16" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="D3" s="15" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="E3" s="15" t="s">
-        <v>139</v>
-      </c>
-      <c r="F3" s="17" t="b">
+        <v>141</v>
+      </c>
+      <c r="F3" s="15" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="G3" s="16" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="30.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="15" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="B4" s="16" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="C4" s="15" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="D4" s="15" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="E4" s="15" t="s">
-        <v>144</v>
-      </c>
-      <c r="F4" s="17" t="b">
+        <v>146</v>
+      </c>
+      <c r="F4" s="15" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="G4" s="16" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="15" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B5" s="16" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="C5" s="15" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="D5" s="15" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="E5" s="15" t="s">
-        <v>150</v>
-      </c>
-      <c r="F5" s="17" t="b">
+        <v>152</v>
+      </c>
+      <c r="F5" s="15" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="G5" s="16" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="15" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="B6" s="16" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C6" s="15" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D6" s="15" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="E6" s="15" t="s">
-        <v>144</v>
-      </c>
-      <c r="F6" s="17" t="b">
+        <v>146</v>
+      </c>
+      <c r="F6" s="15" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="G6" s="16" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="30.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="15" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="B7" s="16" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="C7" s="15" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="D7" s="15" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E7" s="15" t="s">
-        <v>157</v>
-      </c>
-      <c r="F7" s="17" t="b">
+        <v>159</v>
+      </c>
+      <c r="F7" s="15" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="G7" s="16" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
   </sheetData>
@@ -2800,39 +2802,39 @@
         <v>12</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="C2" s="18" t="n">
+        <v>163</v>
+      </c>
+      <c r="C2" s="17" t="n">
         <v>0.3</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="C3" s="18" t="n">
+        <v>165</v>
+      </c>
+      <c r="C3" s="17" t="n">
         <v>0.5</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2" t="s">
-        <v>164</v>
+      <c r="A4" s="3" t="s">
+        <v>166</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="C4" s="18" t="n">
+      <c r="C4" s="17" t="n">
         <v>0.2</v>
       </c>
     </row>

--- a/assets/card_data.xlsx
+++ b/assets/card_data.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="3"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="7"/>
   </bookViews>
   <sheets>
     <sheet name="人物" sheetId="1" state="visible" r:id="rId3"/>
@@ -17,6 +17,7 @@
     <sheet name="合成索引表" sheetId="7" state="visible" r:id="rId9"/>
     <sheet name="read_me" sheetId="8" state="visible" r:id="rId10"/>
     <sheet name="场景" sheetId="9" state="visible" r:id="rId11"/>
+    <sheet name="敌人" sheetId="10" state="visible" r:id="rId12"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -28,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="188">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="384" uniqueCount="254">
   <si>
     <t xml:space="preserve">name</t>
   </si>
@@ -248,7 +249,7 @@
     <t xml:space="preserve">ATK+9</t>
   </si>
   <si>
-    <t xml:space="preserve">骨头*骨头*化石树的树枝*石头</t>
+    <t xml:space="preserve">骨头*骨头*蛛丝</t>
   </si>
   <si>
     <t xml:space="preserve">祈愿者的盖子</t>
@@ -682,6 +683,108 @@
     <t xml:space="preserve">TURE</t>
   </si>
   <si>
+    <t xml:space="preserve">领地意识:远程角色主动出击时不会反击</t>
+  </si>
+  <si>
+    <t xml:space="preserve">群居：主动出击时会在一回合后增加3个同类加入战斗。被动应战时会一次出现三个，总共出现9个</t>
+  </si>
+  <si>
+    <t xml:space="preserve">战斗：①我方回合进行②我方回合结束③敌方回合开始④敌方回合结束</t>
+  </si>
+  <si>
+    <t xml:space="preserve">束缚：使n回合无法行动</t>
+  </si>
+  <si>
+    <t xml:space="preserve">战斗异常</t>
+  </si>
+  <si>
+    <t xml:space="preserve">流血：每回合结束时扣除对应层数的生命</t>
+  </si>
+  <si>
+    <t xml:space="preserve">失明：命中率降低80%，持续n回合</t>
+  </si>
+  <si>
+    <t xml:space="preserve">头晕：命中率降低10%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">上升诅咒1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">恶心：命中率降低30%，ATK-30%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">麻痹：ATK-80%，n+1回合行动一次</t>
+  </si>
+  <si>
+    <t xml:space="preserve">失衡幻听：无法行动</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">七窍流血：随时间推移失去</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">95%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">的</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">HP</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">五感丧失：永久失去行动能力</t>
+  </si>
+  <si>
+    <t xml:space="preserve">极度混乱：永久自残或伤害他人</t>
+  </si>
+  <si>
+    <t xml:space="preserve">生骸：丧失人性</t>
+  </si>
+  <si>
+    <t xml:space="preserve">死亡：永久死亡</t>
+  </si>
+  <si>
+    <t xml:space="preserve">鼓舞：ATK提高30%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">正面效果</t>
+  </si>
+  <si>
+    <t xml:space="preserve">白笛激发：激发遗物真正的功能</t>
+  </si>
+  <si>
+    <t xml:space="preserve">免疫诅咒：免疫n层诅咒效果</t>
+  </si>
+  <si>
     <t xml:space="preserve">出现概率</t>
   </si>
   <si>
@@ -698,6 +801,160 @@
   </si>
   <si>
     <t xml:space="preserve">草原</t>
+  </si>
+  <si>
+    <t xml:space="preserve">出现地点</t>
+  </si>
+  <si>
+    <t xml:space="preserve">特性</t>
+  </si>
+  <si>
+    <t xml:space="preserve">掉落物</t>
+  </si>
+  <si>
+    <t xml:space="preserve">攻击模式</t>
+  </si>
+  <si>
+    <t xml:space="preserve">可被驯服</t>
+  </si>
+  <si>
+    <t xml:space="preserve">敌人</t>
+  </si>
+  <si>
+    <t xml:space="preserve">毒针线虫 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">layer1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">领地意识</t>
+  </si>
+  <si>
+    <t xml:space="preserve">蛛丝</t>
+  </si>
+  <si>
+    <t xml:space="preserve">毒液</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[{“单体””伤害”:6},{“单体”“施加效果”:吐蛛丝}]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">槌嘴鸟 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Layer1-4</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="等线"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">骨头,鸟肉,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="等线"/>
+        <family val="0"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">打火石</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">泣尸鸟 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">layer2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">群居</t>
+  </si>
+  <si>
+    <t xml:space="preserve">捕捉动物并起飞使其受到上升诅咒</t>
+  </si>
+  <si>
+    <t xml:space="preserve">幼鸟</t>
+  </si>
+  <si>
+    <t xml:space="preserve">血口大蛇 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Layer1-3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">捕风猴 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">领地意识,群居</t>
+  </si>
+  <si>
+    <t xml:space="preserve">扔石头</t>
+  </si>
+  <si>
+    <t xml:space="preserve">毯毯鼠</t>
+  </si>
+  <si>
+    <t xml:space="preserve">layer3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">鲜美的肉</t>
+  </si>
+  <si>
+    <t xml:space="preserve">穿弹兽 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">layer4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">领地意识,百分百闪避</t>
+  </si>
+  <si>
+    <t xml:space="preserve">毒针*50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">穿刺，中毒</t>
+  </si>
+  <si>
+    <t xml:space="preserve">鬼锤嘴鸟 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">竹熊 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">水菇</t>
+  </si>
+  <si>
+    <t xml:space="preserve">七条尾巴的大蝎子 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">layer5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">巢穴</t>
+  </si>
+  <si>
+    <t xml:space="preserve">溶骨毒</t>
+  </si>
+  <si>
+    <t xml:space="preserve">龙鬃螺鸩 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">layer6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">鳞甲有毒，</t>
+  </si>
+  <si>
+    <t xml:space="preserve">空前蜥 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">异常美味的蛋</t>
   </si>
 </sst>
 </file>
@@ -708,7 +965,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="0%"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="17">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -806,8 +1063,29 @@
       <family val="0"/>
       <charset val="1"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="等线"/>
+      <family val="0"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="134"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="13">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -824,6 +1102,60 @@
       <patternFill patternType="solid">
         <fgColor theme="8" tint="0.7999"/>
         <bgColor rgb="FFE2F0D9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE8F2A1"/>
+        <bgColor rgb="FFFFFFA6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFD8CE"/>
+        <bgColor rgb="FFE2F0D9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFD7"/>
+        <bgColor rgb="FFFFFFA6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF6D"/>
+        <bgColor rgb="FFFFFF38"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFA6"/>
+        <bgColor rgb="FFE8F2A1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF38"/>
+        <bgColor rgb="FFFFFF6D"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFACB20C"/>
+        <bgColor rgb="FF77BC65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF706E0C"/>
+        <bgColor rgb="FF808080"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF77BC65"/>
+        <bgColor rgb="FFACB20C"/>
       </patternFill>
     </fill>
   </fills>
@@ -861,93 +1193,157 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="38">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="justify" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="justify" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="justify" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="justify" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="9" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="9" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="10" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="11" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="9" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="12" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="0" fillId="9" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="15" fillId="12" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="justify" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -962,24 +1358,24 @@
   <colors>
     <indexedColors>
       <rgbColor rgb="FF000000"/>
-      <rgbColor rgb="FFFFFFFF"/>
+      <rgbColor rgb="FFE8F2A1"/>
       <rgbColor rgb="FFFF0000"/>
       <rgbColor rgb="FF00FF00"/>
       <rgbColor rgb="FF0000FF"/>
-      <rgbColor rgb="FFFFFF00"/>
+      <rgbColor rgb="FFFFFF38"/>
       <rgbColor rgb="FFFF00FF"/>
       <rgbColor rgb="FF00FFFF"/>
       <rgbColor rgb="FF800000"/>
       <rgbColor rgb="FF008000"/>
       <rgbColor rgb="FF000080"/>
-      <rgbColor rgb="FF808000"/>
+      <rgbColor rgb="FF706E0C"/>
       <rgbColor rgb="FF800080"/>
       <rgbColor rgb="FF008080"/>
       <rgbColor rgb="FFC0C0C0"/>
       <rgbColor rgb="FF808080"/>
       <rgbColor rgb="FF9999FF"/>
       <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FFFFFFCC"/>
+      <rgbColor rgb="FFFFFFD7"/>
       <rgbColor rgb="FFCCFFFF"/>
       <rgbColor rgb="FF660066"/>
       <rgbColor rgb="FFFF8080"/>
@@ -987,7 +1383,7 @@
       <rgbColor rgb="FFDAE3F3"/>
       <rgbColor rgb="FF000080"/>
       <rgbColor rgb="FFFF00FF"/>
-      <rgbColor rgb="FFFFFF00"/>
+      <rgbColor rgb="FFFFFF6D"/>
       <rgbColor rgb="FF00FFFF"/>
       <rgbColor rgb="FF800080"/>
       <rgbColor rgb="FF800000"/>
@@ -996,19 +1392,19 @@
       <rgbColor rgb="FF00CCFF"/>
       <rgbColor rgb="FFCCFFFF"/>
       <rgbColor rgb="FFE2F0D9"/>
-      <rgbColor rgb="FFFFFF99"/>
+      <rgbColor rgb="FFFFFFA6"/>
       <rgbColor rgb="FF99CCFF"/>
       <rgbColor rgb="FFFF99CC"/>
       <rgbColor rgb="FFCC99FF"/>
-      <rgbColor rgb="FFFFCC99"/>
+      <rgbColor rgb="FFFFD8CE"/>
       <rgbColor rgb="FF3366FF"/>
       <rgbColor rgb="FF33CCCC"/>
-      <rgbColor rgb="FF99CC00"/>
+      <rgbColor rgb="FFACB20C"/>
       <rgbColor rgb="FFFFCC00"/>
       <rgbColor rgb="FFFF9900"/>
       <rgbColor rgb="FFFF6600"/>
       <rgbColor rgb="FF666699"/>
-      <rgbColor rgb="FF969696"/>
+      <rgbColor rgb="FF77BC65"/>
       <rgbColor rgb="FF003366"/>
       <rgbColor rgb="FF339966"/>
       <rgbColor rgb="FF003300"/>
@@ -1224,25 +1620,25 @@
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="0" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="0" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="0" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="0" t="s">
+      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="0" t="s">
+      <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="0" t="s">
+      <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="0" t="s">
+      <c r="L1" s="2" t="s">
         <v>11</v>
       </c>
       <c r="M1" s="1" t="s">
@@ -1268,13 +1664,13 @@
       <c r="F2" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="G2" s="3" t="s">
         <v>16</v>
       </c>
       <c r="M2" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="T2" s="3" t="s">
+      <c r="T2" s="4" t="s">
         <v>18</v>
       </c>
     </row>
@@ -1294,7 +1690,7 @@
       <c r="M3" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="T3" s="3" t="s">
+      <c r="T3" s="4" t="s">
         <v>21</v>
       </c>
     </row>
@@ -1325,6 +1721,227 @@
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:M13"/>
+  <sheetFormatPr defaultColWidth="11.03515625" defaultRowHeight="13.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="7.88"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="13.01"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="11.3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="4.35"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="36.45"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="33.55"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="B1" s="0" t="s">
+        <v>209</v>
+      </c>
+      <c r="C1" s="0" t="s">
+        <v>210</v>
+      </c>
+      <c r="D1" s="0" t="s">
+        <v>211</v>
+      </c>
+      <c r="F1" s="0" t="s">
+        <v>212</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="J1" s="0" t="s">
+        <v>213</v>
+      </c>
+      <c r="M1" s="31" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="32" t="s">
+        <v>215</v>
+      </c>
+      <c r="B2" s="0" t="s">
+        <v>216</v>
+      </c>
+      <c r="C2" s="0" t="s">
+        <v>217</v>
+      </c>
+      <c r="D2" s="0" t="s">
+        <v>218</v>
+      </c>
+      <c r="E2" s="0" t="s">
+        <v>219</v>
+      </c>
+      <c r="F2" s="0" t="s">
+        <v>220</v>
+      </c>
+      <c r="G2" s="0" t="n">
+        <v>30</v>
+      </c>
+      <c r="H2" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="I2" s="0" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="33" t="s">
+        <v>221</v>
+      </c>
+      <c r="B3" s="0" t="s">
+        <v>222</v>
+      </c>
+      <c r="D3" s="0" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="34" t="s">
+        <v>224</v>
+      </c>
+      <c r="B4" s="0" t="s">
+        <v>225</v>
+      </c>
+      <c r="C4" s="0" t="s">
+        <v>226</v>
+      </c>
+      <c r="F4" s="0" t="s">
+        <v>227</v>
+      </c>
+      <c r="J4" s="0" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="35" t="s">
+        <v>229</v>
+      </c>
+      <c r="B5" s="0" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="35" t="s">
+        <v>231</v>
+      </c>
+      <c r="B6" s="0" t="s">
+        <v>225</v>
+      </c>
+      <c r="C6" s="0" t="s">
+        <v>232</v>
+      </c>
+      <c r="F6" s="0" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="36" t="s">
+        <v>234</v>
+      </c>
+      <c r="B7" s="0" t="s">
+        <v>235</v>
+      </c>
+      <c r="C7" s="0" t="s">
+        <v>226</v>
+      </c>
+      <c r="D7" s="0" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="35" t="s">
+        <v>237</v>
+      </c>
+      <c r="B8" s="0" t="s">
+        <v>238</v>
+      </c>
+      <c r="C8" s="0" t="s">
+        <v>239</v>
+      </c>
+      <c r="D8" s="0" t="s">
+        <v>240</v>
+      </c>
+      <c r="F8" s="0" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="37" t="s">
+        <v>242</v>
+      </c>
+      <c r="B9" s="0" t="s">
+        <v>238</v>
+      </c>
+      <c r="D9" s="0" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="33" t="s">
+        <v>243</v>
+      </c>
+      <c r="D10" s="0" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="35" t="s">
+        <v>245</v>
+      </c>
+      <c r="B11" s="0" t="s">
+        <v>246</v>
+      </c>
+      <c r="C11" s="0" t="s">
+        <v>247</v>
+      </c>
+      <c r="F11" s="0" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="35" t="s">
+        <v>249</v>
+      </c>
+      <c r="B12" s="0" t="s">
+        <v>250</v>
+      </c>
+      <c r="F12" s="0" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="34" t="s">
+        <v>252</v>
+      </c>
+      <c r="D13" s="0" t="s">
+        <v>253</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,标准"&amp;12&amp;Kffffff&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,标准"&amp;12&amp;Kffffff页 &amp;P</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
@@ -1399,7 +2016,7 @@
       <c r="H2" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="I2" s="4" t="b">
+      <c r="I2" s="1" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
@@ -1426,7 +2043,7 @@
       <c r="H3" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="I3" s="4" t="b">
+      <c r="I3" s="1" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
@@ -1447,7 +2064,7 @@
       <c r="D4" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="E4" s="3" t="s">
         <v>41</v>
       </c>
       <c r="G4" s="1" t="n">
@@ -1456,7 +2073,7 @@
       <c r="H4" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="I4" s="4" t="b">
+      <c r="I4" s="1" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
@@ -1483,7 +2100,7 @@
       <c r="H5" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="I5" s="4" t="b">
+      <c r="I5" s="1" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
@@ -1492,7 +2109,7 @@
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="2" t="s">
+      <c r="A6" s="3" t="s">
         <v>44</v>
       </c>
       <c r="B6" s="1" t="s">
@@ -1510,7 +2127,7 @@
       <c r="H6" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="I6" s="4" t="b">
+      <c r="I6" s="1" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
@@ -1540,7 +2157,7 @@
       <c r="H7" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="I7" s="4" t="b">
+      <c r="I7" s="1" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
@@ -1570,7 +2187,7 @@
       <c r="H8" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="I8" s="4" t="b">
+      <c r="I8" s="1" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
@@ -1600,7 +2217,7 @@
       <c r="H9" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="I9" s="4" t="b">
+      <c r="I9" s="1" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
@@ -1630,7 +2247,7 @@
       <c r="H10" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="I10" s="4" t="b">
+      <c r="I10" s="1" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
@@ -1657,7 +2274,7 @@
       <c r="H11" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="I11" s="4" t="b">
+      <c r="I11" s="1" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
@@ -1678,14 +2295,14 @@
       <c r="D12" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="E12" s="2"/>
+      <c r="E12" s="3"/>
       <c r="G12" s="1" t="n">
         <v>11</v>
       </c>
       <c r="H12" s="1" t="n">
         <v>100</v>
       </c>
-      <c r="I12" s="4" t="b">
+      <c r="I12" s="1" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
@@ -1697,7 +2314,7 @@
       <c r="A13" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="B13" s="3" t="s">
         <v>40</v>
       </c>
       <c r="C13" s="1" t="n">
@@ -1712,7 +2329,7 @@
       <c r="H13" s="1" t="n">
         <v>20</v>
       </c>
-      <c r="I13" s="4" t="b">
+      <c r="I13" s="1" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
@@ -1741,7 +2358,7 @@
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="14.13"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="3" min="2" style="1" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="30.25"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="2" width="30.25"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="7" min="6" style="1" width="10"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="6.63"/>
   </cols>
@@ -1756,10 +2373,10 @@
       <c r="C1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="D1" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="E1" s="0" t="s">
+      <c r="E1" s="2" t="s">
         <v>30</v>
       </c>
       <c r="F1" s="1" t="s">
@@ -1782,7 +2399,7 @@
       <c r="C2" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="D2" s="0" t="n">
+      <c r="D2" s="2" t="n">
         <v>13</v>
       </c>
       <c r="F2" s="1" t="n">
@@ -1805,7 +2422,7 @@
       <c r="C3" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="D3" s="0" t="n">
+      <c r="D3" s="2" t="n">
         <v>14</v>
       </c>
       <c r="F3" s="1" t="n">
@@ -1828,7 +2445,7 @@
       <c r="C4" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="D4" s="0" t="n">
+      <c r="D4" s="2" t="n">
         <v>15</v>
       </c>
       <c r="F4" s="1" t="n">
@@ -1851,10 +2468,10 @@
       <c r="C5" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="D5" s="0" t="n">
+      <c r="D5" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="E5" s="0" t="s">
+      <c r="E5" s="2" t="s">
         <v>67</v>
       </c>
       <c r="F5" s="1" t="n">
@@ -1877,10 +2494,10 @@
       <c r="C6" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="D6" s="0" t="n">
+      <c r="D6" s="2" t="n">
         <v>17</v>
       </c>
-      <c r="E6" s="0" t="s">
+      <c r="E6" s="2" t="s">
         <v>70</v>
       </c>
       <c r="F6" s="1" t="n">
@@ -1903,7 +2520,7 @@
       <c r="C7" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D7" s="0" t="n">
+      <c r="D7" s="2" t="n">
         <v>18</v>
       </c>
       <c r="F7" s="1" t="n">
@@ -1926,7 +2543,7 @@
       <c r="C8" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="D8" s="0" t="n">
+      <c r="D8" s="2" t="n">
         <v>20</v>
       </c>
       <c r="F8" s="1" t="n">
@@ -1949,7 +2566,7 @@
       <c r="C9" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="D9" s="0" t="n">
+      <c r="D9" s="2" t="n">
         <v>21</v>
       </c>
       <c r="E9" s="7" t="s">
@@ -1958,7 +2575,7 @@
       <c r="F9" s="1" t="n">
         <v>150</v>
       </c>
-      <c r="G9" s="4" t="b">
+      <c r="G9" s="1" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
@@ -1976,7 +2593,7 @@
       <c r="C10" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="D10" s="0" t="n">
+      <c r="D10" s="2" t="n">
         <v>22</v>
       </c>
       <c r="E10" s="8" t="s">
@@ -2002,7 +2619,7 @@
       <c r="C11" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="D11" s="0" t="n">
+      <c r="D11" s="2" t="n">
         <v>23</v>
       </c>
       <c r="E11" s="8" t="s">
@@ -2028,7 +2645,7 @@
       <c r="C12" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D12" s="0" t="n">
+      <c r="D12" s="2" t="n">
         <v>24</v>
       </c>
       <c r="E12" s="7" t="s">
@@ -2054,13 +2671,13 @@
       <c r="C13" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="D13" s="0" t="n">
+      <c r="D13" s="2" t="n">
         <v>25</v>
       </c>
       <c r="F13" s="1" t="n">
         <v>120</v>
       </c>
-      <c r="G13" s="4" t="b">
+      <c r="G13" s="1" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
@@ -2092,9 +2709,9 @@
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="10"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="11.88"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="6" min="5" style="1" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="25.87"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="17.81"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16377" style="0" width="11.04"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="2" width="25.87"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="2" width="17.81"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16377" style="2" width="11.05"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2116,16 +2733,16 @@
       <c r="F1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="G1" s="0" t="s">
+      <c r="G1" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="H1" s="0" t="s">
+      <c r="H1" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="I1" s="0" t="s">
+      <c r="I1" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="J1" s="0" t="s">
+      <c r="J1" s="2" t="s">
         <v>95</v>
       </c>
     </row>
@@ -2145,7 +2762,7 @@
       <c r="F2" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="G2" s="0" t="s">
+      <c r="G2" s="2" t="s">
         <v>97</v>
       </c>
     </row>
@@ -2156,7 +2773,7 @@
       <c r="B3" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="D3" s="4" t="b">
+      <c r="D3" s="1" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
@@ -2166,13 +2783,13 @@
       <c r="F3" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="H3" s="0" t="s">
+      <c r="H3" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="I3" s="0" t="s">
+      <c r="I3" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="J3" s="0" t="s">
+      <c r="J3" s="2" t="s">
         <v>102</v>
       </c>
     </row>
@@ -2183,7 +2800,8 @@
       <c r="B4" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="D4" s="4" t="b">
+      <c r="D4" s="1" t="b">
+        <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="E4" s="1" t="n">
@@ -2192,7 +2810,7 @@
       <c r="F4" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="G4" s="0" t="s">
+      <c r="G4" s="2" t="s">
         <v>105</v>
       </c>
     </row>
@@ -2203,7 +2821,8 @@
       <c r="B5" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="D5" s="4" t="b">
+      <c r="D5" s="1" t="b">
+        <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="E5" s="1" t="n">
@@ -2212,13 +2831,13 @@
       <c r="F5" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="H5" s="0" t="s">
+      <c r="H5" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="I5" s="0" t="s">
+      <c r="I5" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="J5" s="0" t="s">
+      <c r="J5" s="2" t="s">
         <v>109</v>
       </c>
     </row>
@@ -2229,7 +2848,8 @@
       <c r="B6" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="D6" s="4" t="b">
+      <c r="D6" s="1" t="b">
+        <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="E6" s="1" t="n">
@@ -2238,13 +2858,13 @@
       <c r="F6" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="H6" s="0" t="s">
+      <c r="H6" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="I6" s="0" t="s">
+      <c r="I6" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="J6" s="0" t="s">
+      <c r="J6" s="2" t="s">
         <v>102</v>
       </c>
     </row>
@@ -2255,7 +2875,8 @@
       <c r="B7" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="D7" s="4" t="b">
+      <c r="D7" s="1" t="b">
+        <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="E7" s="1" t="n">
@@ -2264,13 +2885,13 @@
       <c r="F7" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="H7" s="0" t="n">
+      <c r="H7" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="I7" s="0" t="s">
+      <c r="I7" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="J7" s="0" t="s">
+      <c r="J7" s="2" t="s">
         <v>116</v>
       </c>
     </row>
@@ -2448,80 +3069,80 @@
   <sheetFormatPr defaultColWidth="11.75390625" defaultRowHeight="13.5" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="D1" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="E1" s="0" t="s">
+      <c r="E1" s="2" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="A2" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="C2" s="0" t="n">
+      <c r="C2" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="E2" s="0" t="s">
+      <c r="E2" s="2" t="s">
         <v>138</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+      <c r="A3" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="B3" s="0" t="s">
+      <c r="B3" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="C3" s="0" t="n">
+      <c r="C3" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="D3" s="0" t="n">
+      <c r="D3" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E3" s="0" t="s">
+      <c r="E3" s="2" t="s">
         <v>138</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+      <c r="A4" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="B4" s="0" t="s">
+      <c r="B4" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="C4" s="0" t="n">
+      <c r="C4" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="E4" s="0" t="s">
+      <c r="E4" s="2" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+      <c r="A5" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="B5" s="0" t="s">
+      <c r="B5" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="C5" s="0" t="n">
+      <c r="C5" s="2" t="n">
         <v>1000</v>
       </c>
-      <c r="E5" s="0" t="s">
+      <c r="E5" s="2" t="s">
         <v>143</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
+      <c r="A7" s="2" t="s">
         <v>144</v>
       </c>
     </row>
@@ -2544,7 +3165,7 @@
   <dimension ref="A1:C25"/>
   <sheetFormatPr defaultColWidth="9.00390625" defaultRowHeight="13.5" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="14.13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="2" width="14.13"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2554,7 +3175,7 @@
       <c r="B1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" s="2" t="s">
         <v>145</v>
       </c>
     </row>
@@ -2766,16 +3387,16 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G1048576"/>
   <sheetFormatPr defaultColWidth="9.00390625" defaultRowHeight="13.5" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="9.63"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="50.63"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="18.5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="28.25"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="49.63"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="50.63"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="2" width="42.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="50.63"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="2" width="18.5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="2" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="2" width="28.25"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="2" width="49.63"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="2" width="50.63"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2828,7 +3449,7 @@
       <c r="E3" s="18" t="s">
         <v>160</v>
       </c>
-      <c r="F3" s="20" t="b">
+      <c r="F3" s="18" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
@@ -2852,7 +3473,7 @@
       <c r="E4" s="18" t="s">
         <v>165</v>
       </c>
-      <c r="F4" s="20" t="b">
+      <c r="F4" s="18" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
@@ -2876,7 +3497,7 @@
       <c r="E5" s="18" t="s">
         <v>171</v>
       </c>
-      <c r="F5" s="20" t="b">
+      <c r="F5" s="18" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
@@ -2900,7 +3521,7 @@
       <c r="E6" s="18" t="s">
         <v>165</v>
       </c>
-      <c r="F6" s="20" t="b">
+      <c r="F6" s="18" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
@@ -2924,7 +3545,7 @@
       <c r="E7" s="18" t="s">
         <v>178</v>
       </c>
-      <c r="F7" s="20" t="b">
+      <c r="F7" s="18" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
@@ -2953,6 +3574,131 @@
         <v>42</v>
       </c>
     </row>
+    <row r="11" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="20" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="20" t="s">
+        <v>183</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="21" t="s">
+        <v>185</v>
+      </c>
+      <c r="B13" s="22" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="22" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="22" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="23" t="s">
+        <v>189</v>
+      </c>
+      <c r="B16" s="24" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="25" t="s">
+        <v>191</v>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="24" t="s">
+        <v>192</v>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="26" t="s">
+        <v>193</v>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="27" t="s">
+        <v>194</v>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="28" t="s">
+        <v>195</v>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="28" t="s">
+        <v>196</v>
+      </c>
+      <c r="B22" s="2" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="29" t="s">
+        <v>197</v>
+      </c>
+      <c r="B23" s="2" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="29" t="s">
+        <v>198</v>
+      </c>
+      <c r="B24" s="2" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="2" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="2" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="1048573" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048574" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:G1"/>
@@ -2988,39 +3734,39 @@
         <v>12</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>182</v>
+        <v>203</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>183</v>
+        <v>204</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="C2" s="21" t="n">
+        <v>205</v>
+      </c>
+      <c r="C2" s="30" t="n">
         <v>0.3</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>185</v>
+        <v>206</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="C3" s="21" t="n">
+        <v>207</v>
+      </c>
+      <c r="C3" s="30" t="n">
         <v>0.5</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2" t="s">
-        <v>187</v>
+      <c r="A4" s="3" t="s">
+        <v>208</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="C4" s="21" t="n">
+      <c r="C4" s="30" t="n">
         <v>0.2</v>
       </c>
     </row>

--- a/assets/card_data.xlsx
+++ b/assets/card_data.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="7"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="9"/>
   </bookViews>
   <sheets>
     <sheet name="人物" sheetId="1" state="visible" r:id="rId3"/>
@@ -723,9 +723,9 @@
       <rPr>
         <sz val="10"/>
         <color rgb="FF000000"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-        <charset val="134"/>
+        <rFont val="等线"/>
+        <family val="0"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">七窍流血：随时间推移失去</t>
     </r>
@@ -743,9 +743,9 @@
       <rPr>
         <sz val="10"/>
         <color rgb="FF000000"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-        <charset val="134"/>
+        <rFont val="等线"/>
+        <family val="0"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">的</t>
     </r>
@@ -1073,9 +1073,9 @@
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
-      <name val="Segoe UI"/>
-      <family val="2"/>
-      <charset val="134"/>
+      <name val="等线"/>
+      <family val="0"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -1193,7 +1193,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="36">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1274,7 +1274,7 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1310,7 +1310,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="11" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="11" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1318,32 +1318,24 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="9" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="12" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="12" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="9" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="9" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="12" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="15" fillId="12" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -1733,28 +1725,28 @@
   <dimension ref="A1:M13"/>
   <sheetFormatPr defaultColWidth="11.03515625" defaultRowHeight="13.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="7.88"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="13.01"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="11.3"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="4.35"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="36.45"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="33.55"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="31" width="7.88"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="31" width="13.01"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="31" width="11.3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="31" width="4.35"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="31" width="36.45"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="31" width="33.55"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="31" t="s">
         <v>25</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="31" t="s">
         <v>209</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" s="31" t="s">
         <v>210</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="D1" s="31" t="s">
         <v>211</v>
       </c>
-      <c r="F1" s="0" t="s">
+      <c r="F1" s="31" t="s">
         <v>212</v>
       </c>
       <c r="G1" s="1" t="s">
@@ -1766,10 +1758,10 @@
       <c r="I1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="J1" s="0" t="s">
+      <c r="J1" s="31" t="s">
         <v>213</v>
       </c>
-      <c r="M1" s="31" t="s">
+      <c r="M1" s="26" t="s">
         <v>214</v>
       </c>
     </row>
@@ -1777,28 +1769,28 @@
       <c r="A2" s="32" t="s">
         <v>215</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" s="31" t="s">
         <v>216</v>
       </c>
-      <c r="C2" s="0" t="s">
+      <c r="C2" s="31" t="s">
         <v>217</v>
       </c>
-      <c r="D2" s="0" t="s">
+      <c r="D2" s="31" t="s">
         <v>218</v>
       </c>
-      <c r="E2" s="0" t="s">
+      <c r="E2" s="31" t="s">
         <v>219</v>
       </c>
-      <c r="F2" s="0" t="s">
+      <c r="F2" s="31" t="s">
         <v>220</v>
       </c>
-      <c r="G2" s="0" t="n">
+      <c r="G2" s="31" t="n">
         <v>30</v>
       </c>
-      <c r="H2" s="0" t="n">
+      <c r="H2" s="31" t="n">
         <v>6</v>
       </c>
-      <c r="I2" s="0" t="n">
+      <c r="I2" s="31" t="n">
         <v>3</v>
       </c>
     </row>
@@ -1806,91 +1798,91 @@
       <c r="A3" s="33" t="s">
         <v>221</v>
       </c>
-      <c r="B3" s="0" t="s">
+      <c r="B3" s="31" t="s">
         <v>222</v>
       </c>
-      <c r="D3" s="0" t="s">
+      <c r="D3" s="31" t="s">
         <v>223</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="34" t="s">
+      <c r="A4" s="9" t="s">
         <v>224</v>
       </c>
-      <c r="B4" s="0" t="s">
+      <c r="B4" s="31" t="s">
         <v>225</v>
       </c>
-      <c r="C4" s="0" t="s">
+      <c r="C4" s="31" t="s">
         <v>226</v>
       </c>
-      <c r="F4" s="0" t="s">
+      <c r="F4" s="31" t="s">
         <v>227</v>
       </c>
-      <c r="J4" s="0" t="s">
+      <c r="J4" s="31" t="s">
         <v>228</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="35" t="s">
+      <c r="A5" s="34" t="s">
         <v>229</v>
       </c>
-      <c r="B5" s="0" t="s">
+      <c r="B5" s="31" t="s">
         <v>230</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="35" t="s">
+      <c r="A6" s="34" t="s">
         <v>231</v>
       </c>
-      <c r="B6" s="0" t="s">
+      <c r="B6" s="31" t="s">
         <v>225</v>
       </c>
-      <c r="C6" s="0" t="s">
+      <c r="C6" s="31" t="s">
         <v>232</v>
       </c>
-      <c r="F6" s="0" t="s">
+      <c r="F6" s="31" t="s">
         <v>233</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="36" t="s">
+      <c r="A7" s="35" t="s">
         <v>234</v>
       </c>
-      <c r="B7" s="0" t="s">
+      <c r="B7" s="31" t="s">
         <v>235</v>
       </c>
-      <c r="C7" s="0" t="s">
+      <c r="C7" s="31" t="s">
         <v>226</v>
       </c>
-      <c r="D7" s="0" t="s">
+      <c r="D7" s="31" t="s">
         <v>236</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="35" t="s">
+      <c r="A8" s="34" t="s">
         <v>237</v>
       </c>
-      <c r="B8" s="0" t="s">
+      <c r="B8" s="31" t="s">
         <v>238</v>
       </c>
-      <c r="C8" s="0" t="s">
+      <c r="C8" s="31" t="s">
         <v>239</v>
       </c>
-      <c r="D8" s="0" t="s">
+      <c r="D8" s="31" t="s">
         <v>240</v>
       </c>
-      <c r="F8" s="0" t="s">
+      <c r="F8" s="31" t="s">
         <v>241</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="37" t="s">
+      <c r="A9" s="9" t="s">
         <v>242</v>
       </c>
-      <c r="B9" s="0" t="s">
+      <c r="B9" s="31" t="s">
         <v>238</v>
       </c>
-      <c r="D9" s="0" t="s">
+      <c r="D9" s="31" t="s">
         <v>43</v>
       </c>
     </row>
@@ -1898,40 +1890,40 @@
       <c r="A10" s="33" t="s">
         <v>243</v>
       </c>
-      <c r="D10" s="0" t="s">
+      <c r="D10" s="31" t="s">
         <v>244</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="35" t="s">
+      <c r="A11" s="34" t="s">
         <v>245</v>
       </c>
-      <c r="B11" s="0" t="s">
+      <c r="B11" s="31" t="s">
         <v>246</v>
       </c>
-      <c r="C11" s="0" t="s">
+      <c r="C11" s="31" t="s">
         <v>247</v>
       </c>
-      <c r="F11" s="0" t="s">
+      <c r="F11" s="31" t="s">
         <v>248</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="35" t="s">
+      <c r="A12" s="34" t="s">
         <v>249</v>
       </c>
-      <c r="B12" s="0" t="s">
+      <c r="B12" s="31" t="s">
         <v>250</v>
       </c>
-      <c r="F12" s="0" t="s">
+      <c r="F12" s="31" t="s">
         <v>251</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="34" t="s">
+      <c r="A13" s="9" t="s">
         <v>252</v>
       </c>
-      <c r="D13" s="0" t="s">
+      <c r="D13" s="31" t="s">
         <v>253</v>
       </c>
     </row>
@@ -3390,7 +3382,7 @@
   <dimension ref="A1:G1048576"/>
   <sheetFormatPr defaultColWidth="9.00390625" defaultRowHeight="13.5" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="2" width="42.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="2" width="42.52"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="50.63"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="2" width="18.5"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="2" width="14"/>

--- a/assets/card_data.xlsx
+++ b/assets/card_data.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="9"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="人物" sheetId="1" state="visible" r:id="rId3"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="384" uniqueCount="254">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="392" uniqueCount="262">
   <si>
     <t xml:space="preserve">name</t>
   </si>
@@ -68,6 +68,9 @@
   </si>
   <si>
     <t xml:space="preserve">picture_path</t>
+  </si>
+  <si>
+    <t xml:space="preserve">speed</t>
   </si>
   <si>
     <t xml:space="preserve">add_fight_active_skill()</t>
@@ -112,6 +115,27 @@
   </si>
   <si>
     <t xml:space="preserve">res://assets/character/人物_娜娜奇.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">力量影响近战武器的判断成功率</t>
+  </si>
+  <si>
+    <t xml:space="preserve">意识（洞察） </t>
+  </si>
+  <si>
+    <t xml:space="preserve">速度 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">生命</t>
+  </si>
+  <si>
+    <t xml:space="preserve">抗诅咒值</t>
+  </si>
+  <si>
+    <t xml:space="preserve">闪避</t>
+  </si>
+  <si>
+    <t xml:space="preserve">护甲值 </t>
   </si>
   <si>
     <t xml:space="preserve">名称</t>
@@ -965,7 +989,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="0%"/>
   </numFmts>
-  <fonts count="17">
+  <fonts count="19">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -1002,6 +1026,21 @@
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="等线"/>
       <family val="0"/>
       <charset val="1"/>
     </font>
@@ -1193,7 +1232,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="38">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1218,15 +1257,23 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="justify" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="justify" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1250,27 +1297,27 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="justify" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1278,7 +1325,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="16" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1302,7 +1349,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="9" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="17" fillId="9" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1322,7 +1369,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1334,7 +1381,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="12" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="17" fillId="12" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1587,7 +1634,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:T4"/>
+  <dimension ref="A1:T13"/>
   <sheetFormatPr defaultColWidth="10.00390625" defaultRowHeight="14.25" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="4" min="1" style="1" width="10"/>
@@ -1636,13 +1683,16 @@
       <c r="M1" s="1" t="s">
         <v>12</v>
       </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
       <c r="T1" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="77.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B2" s="1" t="n">
         <v>10</v>
@@ -1654,21 +1704,21 @@
         <v>0</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="T2" s="4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="66.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B3" s="1" t="n">
         <v>50</v>
@@ -1680,15 +1730,15 @@
         <v>50</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="T3" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B4" s="1" t="n">
         <v>30</v>
@@ -1700,10 +1750,45 @@
         <v>5</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="6" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="5" t="s">
+        <v>32</v>
       </c>
     </row>
   </sheetData>
@@ -1725,29 +1810,29 @@
   <dimension ref="A1:M13"/>
   <sheetFormatPr defaultColWidth="11.03515625" defaultRowHeight="13.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="31" width="7.88"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="31" width="13.01"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="31" width="11.3"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="31" width="4.35"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="31" width="36.45"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="31" width="33.55"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="33" width="7.88"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="33" width="13.01"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="33" width="11.3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="33" width="4.35"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="33" width="36.45"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="33" width="33.55"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="31" t="s">
-        <v>25</v>
-      </c>
-      <c r="B1" s="31" t="s">
-        <v>209</v>
-      </c>
-      <c r="C1" s="31" t="s">
-        <v>210</v>
-      </c>
-      <c r="D1" s="31" t="s">
-        <v>211</v>
-      </c>
-      <c r="F1" s="31" t="s">
-        <v>212</v>
+      <c r="A1" s="33" t="s">
+        <v>33</v>
+      </c>
+      <c r="B1" s="33" t="s">
+        <v>217</v>
+      </c>
+      <c r="C1" s="33" t="s">
+        <v>218</v>
+      </c>
+      <c r="D1" s="33" t="s">
+        <v>219</v>
+      </c>
+      <c r="F1" s="33" t="s">
+        <v>220</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>1</v>
@@ -1758,173 +1843,173 @@
       <c r="I1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="J1" s="31" t="s">
-        <v>213</v>
-      </c>
-      <c r="M1" s="26" t="s">
-        <v>214</v>
+      <c r="J1" s="33" t="s">
+        <v>221</v>
+      </c>
+      <c r="M1" s="28" t="s">
+        <v>222</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="32" t="s">
-        <v>215</v>
-      </c>
-      <c r="B2" s="31" t="s">
-        <v>216</v>
-      </c>
-      <c r="C2" s="31" t="s">
-        <v>217</v>
-      </c>
-      <c r="D2" s="31" t="s">
-        <v>218</v>
-      </c>
-      <c r="E2" s="31" t="s">
-        <v>219</v>
-      </c>
-      <c r="F2" s="31" t="s">
-        <v>220</v>
-      </c>
-      <c r="G2" s="31" t="n">
+      <c r="A2" s="34" t="s">
+        <v>223</v>
+      </c>
+      <c r="B2" s="33" t="s">
+        <v>224</v>
+      </c>
+      <c r="C2" s="33" t="s">
+        <v>225</v>
+      </c>
+      <c r="D2" s="33" t="s">
+        <v>226</v>
+      </c>
+      <c r="E2" s="33" t="s">
+        <v>227</v>
+      </c>
+      <c r="F2" s="33" t="s">
+        <v>228</v>
+      </c>
+      <c r="G2" s="33" t="n">
         <v>30</v>
       </c>
-      <c r="H2" s="31" t="n">
+      <c r="H2" s="33" t="n">
         <v>6</v>
       </c>
-      <c r="I2" s="31" t="n">
+      <c r="I2" s="33" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="33" t="s">
-        <v>221</v>
-      </c>
-      <c r="B3" s="31" t="s">
-        <v>222</v>
-      </c>
-      <c r="D3" s="31" t="s">
-        <v>223</v>
+      <c r="A3" s="35" t="s">
+        <v>229</v>
+      </c>
+      <c r="B3" s="33" t="s">
+        <v>230</v>
+      </c>
+      <c r="D3" s="33" t="s">
+        <v>231</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="9" t="s">
-        <v>224</v>
-      </c>
-      <c r="B4" s="31" t="s">
-        <v>225</v>
-      </c>
-      <c r="C4" s="31" t="s">
-        <v>226</v>
-      </c>
-      <c r="F4" s="31" t="s">
-        <v>227</v>
-      </c>
-      <c r="J4" s="31" t="s">
-        <v>228</v>
+      <c r="A4" s="11" t="s">
+        <v>232</v>
+      </c>
+      <c r="B4" s="33" t="s">
+        <v>233</v>
+      </c>
+      <c r="C4" s="33" t="s">
+        <v>234</v>
+      </c>
+      <c r="F4" s="33" t="s">
+        <v>235</v>
+      </c>
+      <c r="J4" s="33" t="s">
+        <v>236</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="34" t="s">
-        <v>229</v>
-      </c>
-      <c r="B5" s="31" t="s">
-        <v>230</v>
+      <c r="A5" s="36" t="s">
+        <v>237</v>
+      </c>
+      <c r="B5" s="33" t="s">
+        <v>238</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="34" t="s">
-        <v>231</v>
-      </c>
-      <c r="B6" s="31" t="s">
-        <v>225</v>
-      </c>
-      <c r="C6" s="31" t="s">
-        <v>232</v>
-      </c>
-      <c r="F6" s="31" t="s">
+      <c r="A6" s="36" t="s">
+        <v>239</v>
+      </c>
+      <c r="B6" s="33" t="s">
         <v>233</v>
       </c>
+      <c r="C6" s="33" t="s">
+        <v>240</v>
+      </c>
+      <c r="F6" s="33" t="s">
+        <v>241</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="35" t="s">
+      <c r="A7" s="37" t="s">
+        <v>242</v>
+      </c>
+      <c r="B7" s="33" t="s">
+        <v>243</v>
+      </c>
+      <c r="C7" s="33" t="s">
         <v>234</v>
       </c>
-      <c r="B7" s="31" t="s">
-        <v>235</v>
-      </c>
-      <c r="C7" s="31" t="s">
-        <v>226</v>
-      </c>
-      <c r="D7" s="31" t="s">
-        <v>236</v>
+      <c r="D7" s="33" t="s">
+        <v>244</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="34" t="s">
-        <v>237</v>
-      </c>
-      <c r="B8" s="31" t="s">
-        <v>238</v>
-      </c>
-      <c r="C8" s="31" t="s">
-        <v>239</v>
-      </c>
-      <c r="D8" s="31" t="s">
-        <v>240</v>
-      </c>
-      <c r="F8" s="31" t="s">
-        <v>241</v>
+      <c r="A8" s="36" t="s">
+        <v>245</v>
+      </c>
+      <c r="B8" s="33" t="s">
+        <v>246</v>
+      </c>
+      <c r="C8" s="33" t="s">
+        <v>247</v>
+      </c>
+      <c r="D8" s="33" t="s">
+        <v>248</v>
+      </c>
+      <c r="F8" s="33" t="s">
+        <v>249</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="9" t="s">
-        <v>242</v>
-      </c>
-      <c r="B9" s="31" t="s">
-        <v>238</v>
-      </c>
-      <c r="D9" s="31" t="s">
-        <v>43</v>
+      <c r="A9" s="11" t="s">
+        <v>250</v>
+      </c>
+      <c r="B9" s="33" t="s">
+        <v>246</v>
+      </c>
+      <c r="D9" s="33" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="33" t="s">
-        <v>243</v>
-      </c>
-      <c r="D10" s="31" t="s">
-        <v>244</v>
+      <c r="A10" s="35" t="s">
+        <v>251</v>
+      </c>
+      <c r="D10" s="33" t="s">
+        <v>252</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="34" t="s">
-        <v>245</v>
-      </c>
-      <c r="B11" s="31" t="s">
-        <v>246</v>
-      </c>
-      <c r="C11" s="31" t="s">
-        <v>247</v>
-      </c>
-      <c r="F11" s="31" t="s">
-        <v>248</v>
+      <c r="A11" s="36" t="s">
+        <v>253</v>
+      </c>
+      <c r="B11" s="33" t="s">
+        <v>254</v>
+      </c>
+      <c r="C11" s="33" t="s">
+        <v>255</v>
+      </c>
+      <c r="F11" s="33" t="s">
+        <v>256</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="34" t="s">
-        <v>249</v>
-      </c>
-      <c r="B12" s="31" t="s">
-        <v>250</v>
-      </c>
-      <c r="F12" s="31" t="s">
-        <v>251</v>
+      <c r="A12" s="36" t="s">
+        <v>257</v>
+      </c>
+      <c r="B12" s="33" t="s">
+        <v>258</v>
+      </c>
+      <c r="F12" s="33" t="s">
+        <v>259</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="9" t="s">
-        <v>252</v>
-      </c>
-      <c r="D13" s="31" t="s">
-        <v>253</v>
+      <c r="A13" s="11" t="s">
+        <v>260</v>
+      </c>
+      <c r="D13" s="33" t="s">
+        <v>261</v>
       </c>
     </row>
   </sheetData>
@@ -1959,31 +2044,31 @@
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>12</v>
@@ -1991,10 +2076,10 @@
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="C2" s="1" t="n">
         <v>1</v>
@@ -2013,15 +2098,15 @@
         <v>0</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="C3" s="1" t="n">
         <v>1</v>
@@ -2040,15 +2125,15 @@
         <v>0</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="C4" s="1" t="n">
         <v>0</v>
@@ -2057,7 +2142,7 @@
         <v>0</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="G4" s="1" t="n">
         <v>3</v>
@@ -2070,15 +2155,15 @@
         <v>0</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="C5" s="1" t="n">
         <v>0</v>
@@ -2097,15 +2182,15 @@
         <v>0</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="C6" s="1" t="n">
         <v>0</v>
@@ -2124,15 +2209,15 @@
         <v>0</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="C7" s="1" t="n">
         <v>2</v>
@@ -2141,7 +2226,7 @@
         <v>0</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="G7" s="1" t="n">
         <v>6</v>
@@ -2154,15 +2239,15 @@
         <v>0</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="C8" s="1" t="n">
         <v>2</v>
@@ -2171,7 +2256,7 @@
         <v>0</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="G8" s="1" t="n">
         <v>7</v>
@@ -2184,15 +2269,15 @@
         <v>0</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="C9" s="1" t="n">
         <v>6</v>
@@ -2200,8 +2285,8 @@
       <c r="D9" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="F9" s="5" t="s">
-        <v>50</v>
+      <c r="F9" s="7" t="s">
+        <v>58</v>
       </c>
       <c r="G9" s="1" t="n">
         <v>8</v>
@@ -2214,15 +2299,15 @@
         <v>0</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="C10" s="1" t="n">
         <v>3</v>
@@ -2230,8 +2315,8 @@
       <c r="D10" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="F10" s="5" t="s">
-        <v>52</v>
+      <c r="F10" s="7" t="s">
+        <v>60</v>
       </c>
       <c r="G10" s="1" t="n">
         <v>9</v>
@@ -2244,15 +2329,15 @@
         <v>0</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="C11" s="1" t="n">
         <v>0</v>
@@ -2271,15 +2356,15 @@
         <v>0</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="5" t="s">
-        <v>54</v>
+      <c r="A12" s="7" t="s">
+        <v>62</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="C12" s="1" t="n">
         <v>0</v>
@@ -2299,15 +2384,15 @@
         <v>1</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="6" t="s">
-        <v>16</v>
+      <c r="A13" s="8" t="s">
+        <v>17</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="C13" s="1" t="n">
         <v>0</v>
@@ -2326,7 +2411,7 @@
         <v>0</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
     </row>
   </sheetData>
@@ -2357,25 +2442,25 @@
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>12</v>
@@ -2383,13 +2468,13 @@
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="D2" s="2" t="n">
         <v>13</v>
@@ -2398,21 +2483,21 @@
         <v>5</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="D3" s="2" t="n">
         <v>14</v>
@@ -2421,21 +2506,21 @@
         <v>6</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="D4" s="2" t="n">
         <v>15</v>
@@ -2444,73 +2529,73 @@
         <v>7</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="5" t="s">
-        <v>15</v>
+      <c r="A5" s="7" t="s">
+        <v>16</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="D5" s="2" t="n">
         <v>16</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="F5" s="1" t="n">
         <v>8</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="D6" s="2" t="n">
         <v>17</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="F6" s="1" t="n">
         <v>90</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="D7" s="2" t="n">
         <v>18</v>
@@ -2519,21 +2604,21 @@
         <v>10</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="D8" s="2" t="n">
         <v>20</v>
@@ -2542,27 +2627,27 @@
         <v>1</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="D9" s="2" t="n">
         <v>21</v>
       </c>
-      <c r="E9" s="7" t="s">
-        <v>77</v>
+      <c r="E9" s="9" t="s">
+        <v>85</v>
       </c>
       <c r="F9" s="1" t="n">
         <v>150</v>
@@ -2572,96 +2657,96 @@
         <v>1</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="7" t="s">
-        <v>78</v>
+      <c r="A10" s="9" t="s">
+        <v>86</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="D10" s="2" t="n">
         <v>22</v>
       </c>
-      <c r="E10" s="8" t="s">
-        <v>80</v>
+      <c r="E10" s="10" t="s">
+        <v>88</v>
       </c>
       <c r="F10" s="1" t="n">
         <v>100</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="7" t="s">
-        <v>81</v>
+      <c r="A11" s="9" t="s">
+        <v>89</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="D11" s="2" t="n">
         <v>23</v>
       </c>
-      <c r="E11" s="8" t="s">
-        <v>83</v>
+      <c r="E11" s="10" t="s">
+        <v>91</v>
       </c>
       <c r="F11" s="1" t="n">
         <v>200</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="D12" s="2" t="n">
         <v>24</v>
       </c>
-      <c r="E12" s="7" t="s">
-        <v>86</v>
+      <c r="E12" s="9" t="s">
+        <v>94</v>
       </c>
       <c r="F12" s="1" t="n">
         <v>60</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="D13" s="2" t="n">
         <v>25</v>
@@ -2674,7 +2759,7 @@
         <v>1</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
     </row>
   </sheetData>
@@ -2708,62 +2793,62 @@
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>12</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="E2" s="1" t="n">
         <v>1</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="D3" s="1" t="b">
         <f aca="false">TRUE()</f>
@@ -2773,24 +2858,24 @@
         <v>200</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>102</v>
+        <v>110</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="9" t="s">
-        <v>103</v>
+      <c r="A4" s="11" t="s">
+        <v>111</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="D4" s="1" t="b">
         <f aca="false">TRUE()</f>
@@ -2800,18 +2885,18 @@
         <v>100</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>107</v>
+        <v>115</v>
       </c>
       <c r="D5" s="1" t="b">
         <f aca="false">TRUE()</f>
@@ -2821,24 +2906,24 @@
         <v>1</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>110</v>
+        <v>118</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="D6" s="1" t="b">
         <f aca="false">TRUE()</f>
@@ -2848,24 +2933,24 @@
         <v>100</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>102</v>
+        <v>110</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="D7" s="1" t="b">
         <f aca="false">TRUE()</f>
@@ -2875,16 +2960,16 @@
         <v>100</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="H7" s="2" t="n">
         <v>1</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>116</v>
+        <v>124</v>
       </c>
     </row>
     <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -2916,33 +3001,33 @@
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>117</v>
+        <v>125</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>118</v>
+        <v>126</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>119</v>
+        <v>127</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="B2" s="1" t="n">
         <v>0</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="E2" s="1" t="n">
         <v>20000</v>
@@ -2950,16 +3035,16 @@
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>121</v>
+        <v>129</v>
       </c>
       <c r="B3" s="1" t="n">
         <v>1</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="E3" s="1" t="n">
         <v>15000</v>
@@ -2967,16 +3052,16 @@
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="B4" s="1" t="n">
         <v>2</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="E4" s="1" t="n">
         <v>10000</v>
@@ -2984,13 +3069,13 @@
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="B5" s="1" t="n">
         <v>4</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="E5" s="1" t="n">
         <v>300</v>
@@ -2998,13 +3083,13 @@
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="B6" s="1" t="n">
         <v>5</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="E6" s="1" t="n">
         <v>100</v>
@@ -3012,13 +3097,13 @@
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>128</v>
+        <v>136</v>
       </c>
       <c r="B7" s="1" t="n">
         <v>4</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>129</v>
+        <v>137</v>
       </c>
       <c r="E7" s="1" t="n">
         <v>300</v>
@@ -3026,16 +3111,16 @@
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>130</v>
+        <v>138</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>132</v>
+        <v>140</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>131</v>
+        <v>139</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3062,38 +3147,38 @@
   <sheetData>
     <row r="1" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B1" s="2" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>134</v>
+        <v>142</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="C2" s="2" t="n">
         <v>2</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>138</v>
+        <v>146</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="C3" s="2" t="n">
         <v>10</v>
@@ -3102,40 +3187,40 @@
         <v>1</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>138</v>
+        <v>146</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="C4" s="2" t="n">
         <v>4</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>141</v>
+        <v>149</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="C5" s="2" t="n">
         <v>1000</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>144</v>
+        <v>152</v>
       </c>
     </row>
   </sheetData>
@@ -3162,204 +3247,204 @@
   <sheetData>
     <row r="1" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>145</v>
+        <v>153</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="10" t="s">
-        <v>146</v>
-      </c>
-      <c r="B2" s="10" t="n">
+      <c r="A2" s="12" t="s">
+        <v>154</v>
+      </c>
+      <c r="B2" s="12" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="10" t="s">
-        <v>147</v>
-      </c>
-      <c r="B3" s="10" t="n">
+      <c r="A3" s="12" t="s">
+        <v>155</v>
+      </c>
+      <c r="B3" s="12" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="B4" s="10" t="n">
+      <c r="A4" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="B4" s="12" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="B5" s="10" t="n">
+      <c r="A5" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="B5" s="12" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="B6" s="10" t="n">
+      <c r="A6" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="B6" s="12" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="B7" s="10" t="n">
+      <c r="A7" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="B7" s="12" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="B8" s="10" t="n">
+      <c r="A8" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="B8" s="12" t="n">
         <v>7</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="10" t="s">
-        <v>49</v>
-      </c>
-      <c r="B9" s="10" t="n">
+      <c r="A9" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="B9" s="12" t="n">
         <v>8</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="10" t="s">
-        <v>51</v>
-      </c>
-      <c r="B10" s="10" t="n">
+      <c r="A10" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="B10" s="12" t="n">
         <v>9</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="10" t="s">
-        <v>53</v>
-      </c>
-      <c r="B11" s="10" t="n">
+      <c r="A11" s="12" t="s">
+        <v>61</v>
+      </c>
+      <c r="B11" s="12" t="n">
         <v>10</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="10" t="s">
-        <v>123</v>
-      </c>
-      <c r="B12" s="10" t="n">
+      <c r="A12" s="12" t="s">
+        <v>131</v>
+      </c>
+      <c r="B12" s="12" t="n">
         <v>11</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="11" t="s">
+      <c r="A13" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="B13" s="12" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="B14" s="15" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="14" t="s">
+        <v>68</v>
+      </c>
+      <c r="B15" s="15" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="14" t="s">
+        <v>72</v>
+      </c>
+      <c r="B16" s="15" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="B13" s="10" t="n">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="B14" s="13" t="n">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="12" t="s">
-        <v>60</v>
-      </c>
-      <c r="B15" s="13" t="n">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="12" t="s">
-        <v>64</v>
-      </c>
-      <c r="B16" s="13" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="B17" s="13" t="n">
+      <c r="B17" s="15" t="n">
         <v>16</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="12" t="s">
-        <v>68</v>
-      </c>
-      <c r="B18" s="13" t="n">
+      <c r="A18" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="B18" s="15" t="n">
         <v>17</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="12" t="s">
-        <v>71</v>
-      </c>
-      <c r="B19" s="13" t="n">
+      <c r="A19" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="B19" s="15" t="n">
         <v>18</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="12" t="s">
-        <v>73</v>
-      </c>
-      <c r="B20" s="13" t="n">
+      <c r="A20" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="B20" s="15" t="n">
         <v>20</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="B21" s="13" t="n">
+      <c r="A21" s="14" t="s">
+        <v>83</v>
+      </c>
+      <c r="B21" s="15" t="n">
         <v>21</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="14" t="s">
-        <v>78</v>
-      </c>
-      <c r="B22" s="13" t="n">
+      <c r="A22" s="16" t="s">
+        <v>86</v>
+      </c>
+      <c r="B22" s="15" t="n">
         <v>22</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="14" t="s">
-        <v>81</v>
-      </c>
-      <c r="B23" s="13" t="n">
+      <c r="A23" s="16" t="s">
+        <v>89</v>
+      </c>
+      <c r="B23" s="15" t="n">
         <v>23</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="12" t="s">
-        <v>84</v>
-      </c>
-      <c r="B24" s="13" t="n">
+      <c r="A24" s="14" t="s">
+        <v>92</v>
+      </c>
+      <c r="B24" s="15" t="n">
         <v>24</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="12" t="s">
-        <v>87</v>
-      </c>
-      <c r="B25" s="13" t="n">
+      <c r="A25" s="14" t="s">
+        <v>95</v>
+      </c>
+      <c r="B25" s="15" t="n">
         <v>25</v>
       </c>
     </row>
@@ -3392,278 +3477,278 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="15" t="s">
-        <v>148</v>
-      </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15"/>
-      <c r="G1" s="15"/>
+      <c r="A1" s="17" t="s">
+        <v>156</v>
+      </c>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="17"/>
     </row>
     <row r="2" customFormat="false" ht="16.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="16" t="s">
-        <v>149</v>
-      </c>
-      <c r="B2" s="17" t="s">
-        <v>150</v>
-      </c>
-      <c r="C2" s="16" t="s">
-        <v>151</v>
-      </c>
-      <c r="D2" s="16" t="s">
-        <v>152</v>
-      </c>
-      <c r="E2" s="16" t="s">
-        <v>153</v>
-      </c>
-      <c r="F2" s="16" t="s">
-        <v>154</v>
-      </c>
-      <c r="G2" s="17" t="s">
-        <v>155</v>
+      <c r="A2" s="18" t="s">
+        <v>157</v>
+      </c>
+      <c r="B2" s="19" t="s">
+        <v>158</v>
+      </c>
+      <c r="C2" s="18" t="s">
+        <v>159</v>
+      </c>
+      <c r="D2" s="18" t="s">
+        <v>160</v>
+      </c>
+      <c r="E2" s="18" t="s">
+        <v>161</v>
+      </c>
+      <c r="F2" s="18" t="s">
+        <v>162</v>
+      </c>
+      <c r="G2" s="19" t="s">
+        <v>163</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="30.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="18" t="s">
-        <v>156</v>
-      </c>
-      <c r="B3" s="19" t="s">
-        <v>157</v>
-      </c>
-      <c r="C3" s="18" t="s">
-        <v>158</v>
-      </c>
-      <c r="D3" s="18" t="s">
-        <v>159</v>
-      </c>
-      <c r="E3" s="18" t="s">
-        <v>160</v>
-      </c>
-      <c r="F3" s="18" t="b">
+      <c r="A3" s="20" t="s">
+        <v>164</v>
+      </c>
+      <c r="B3" s="21" t="s">
+        <v>165</v>
+      </c>
+      <c r="C3" s="20" t="s">
+        <v>166</v>
+      </c>
+      <c r="D3" s="20" t="s">
+        <v>167</v>
+      </c>
+      <c r="E3" s="20" t="s">
+        <v>168</v>
+      </c>
+      <c r="F3" s="20" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
-      <c r="G3" s="19" t="s">
-        <v>161</v>
+      <c r="G3" s="21" t="s">
+        <v>169</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="30.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="18" t="s">
-        <v>162</v>
-      </c>
-      <c r="B4" s="19" t="s">
-        <v>163</v>
-      </c>
-      <c r="C4" s="18" t="s">
-        <v>162</v>
-      </c>
-      <c r="D4" s="18" t="s">
-        <v>164</v>
-      </c>
-      <c r="E4" s="18" t="s">
-        <v>165</v>
-      </c>
-      <c r="F4" s="18" t="b">
+      <c r="A4" s="20" t="s">
+        <v>170</v>
+      </c>
+      <c r="B4" s="21" t="s">
+        <v>171</v>
+      </c>
+      <c r="C4" s="20" t="s">
+        <v>170</v>
+      </c>
+      <c r="D4" s="20" t="s">
+        <v>172</v>
+      </c>
+      <c r="E4" s="20" t="s">
+        <v>173</v>
+      </c>
+      <c r="F4" s="20" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="G4" s="19" t="s">
-        <v>166</v>
+      <c r="G4" s="21" t="s">
+        <v>174</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="18" t="s">
-        <v>167</v>
-      </c>
-      <c r="B5" s="19" t="s">
-        <v>168</v>
-      </c>
-      <c r="C5" s="18" t="s">
-        <v>169</v>
-      </c>
-      <c r="D5" s="18" t="s">
-        <v>170</v>
-      </c>
-      <c r="E5" s="18" t="s">
-        <v>171</v>
-      </c>
-      <c r="F5" s="18" t="b">
+      <c r="A5" s="20" t="s">
+        <v>175</v>
+      </c>
+      <c r="B5" s="21" t="s">
+        <v>176</v>
+      </c>
+      <c r="C5" s="20" t="s">
+        <v>177</v>
+      </c>
+      <c r="D5" s="20" t="s">
+        <v>178</v>
+      </c>
+      <c r="E5" s="20" t="s">
+        <v>179</v>
+      </c>
+      <c r="F5" s="20" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="G5" s="19" t="s">
-        <v>170</v>
+      <c r="G5" s="21" t="s">
+        <v>178</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="18" t="s">
+      <c r="A6" s="20" t="s">
+        <v>180</v>
+      </c>
+      <c r="B6" s="21" t="s">
+        <v>181</v>
+      </c>
+      <c r="C6" s="20" t="s">
+        <v>182</v>
+      </c>
+      <c r="D6" s="20" t="s">
         <v>172</v>
       </c>
-      <c r="B6" s="19" t="s">
+      <c r="E6" s="20" t="s">
         <v>173</v>
       </c>
-      <c r="C6" s="18" t="s">
-        <v>174</v>
-      </c>
-      <c r="D6" s="18" t="s">
-        <v>164</v>
-      </c>
-      <c r="E6" s="18" t="s">
-        <v>165</v>
-      </c>
-      <c r="F6" s="18" t="b">
+      <c r="F6" s="20" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="G6" s="19" t="s">
-        <v>170</v>
+      <c r="G6" s="21" t="s">
+        <v>178</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="30.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="18" t="s">
-        <v>175</v>
-      </c>
-      <c r="B7" s="19" t="s">
-        <v>176</v>
-      </c>
-      <c r="C7" s="18" t="s">
-        <v>158</v>
-      </c>
-      <c r="D7" s="18" t="s">
-        <v>177</v>
-      </c>
-      <c r="E7" s="18" t="s">
-        <v>178</v>
-      </c>
-      <c r="F7" s="18" t="b">
+      <c r="A7" s="20" t="s">
+        <v>183</v>
+      </c>
+      <c r="B7" s="21" t="s">
+        <v>184</v>
+      </c>
+      <c r="C7" s="20" t="s">
+        <v>166</v>
+      </c>
+      <c r="D7" s="20" t="s">
+        <v>185</v>
+      </c>
+      <c r="E7" s="20" t="s">
+        <v>186</v>
+      </c>
+      <c r="F7" s="20" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
-      <c r="G7" s="19" t="s">
-        <v>179</v>
+      <c r="G7" s="21" t="s">
+        <v>187</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>128</v>
+        <v>136</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>129</v>
+        <v>137</v>
       </c>
       <c r="C10" s="1"/>
       <c r="D10" s="1" t="s">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="F10" s="1" t="n">
         <v>300</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="20" t="s">
-        <v>182</v>
+      <c r="A11" s="22" t="s">
+        <v>190</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="20" t="s">
-        <v>183</v>
+      <c r="A12" s="22" t="s">
+        <v>191</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>184</v>
+        <v>192</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="21" t="s">
-        <v>185</v>
-      </c>
-      <c r="B13" s="22" t="s">
-        <v>186</v>
+      <c r="A13" s="23" t="s">
+        <v>193</v>
+      </c>
+      <c r="B13" s="24" t="s">
+        <v>194</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="22" t="s">
-        <v>187</v>
+      <c r="A14" s="24" t="s">
+        <v>195</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="22" t="s">
-        <v>188</v>
+      <c r="A15" s="24" t="s">
+        <v>196</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="23" t="s">
-        <v>189</v>
-      </c>
-      <c r="B16" s="24" t="s">
-        <v>190</v>
+      <c r="A16" s="25" t="s">
+        <v>197</v>
+      </c>
+      <c r="B16" s="26" t="s">
+        <v>198</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="25" t="s">
-        <v>191</v>
+      <c r="A17" s="27" t="s">
+        <v>199</v>
       </c>
       <c r="B17" s="2" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="24" t="s">
-        <v>192</v>
+      <c r="A18" s="26" t="s">
+        <v>200</v>
       </c>
       <c r="B18" s="2" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="26" t="s">
-        <v>193</v>
+      <c r="A19" s="28" t="s">
+        <v>201</v>
       </c>
       <c r="B19" s="2" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="27" t="s">
-        <v>194</v>
+      <c r="A20" s="29" t="s">
+        <v>202</v>
       </c>
       <c r="B20" s="2" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="28" t="s">
-        <v>195</v>
+      <c r="A21" s="30" t="s">
+        <v>203</v>
       </c>
       <c r="B21" s="2" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="28" t="s">
-        <v>196</v>
+      <c r="A22" s="30" t="s">
+        <v>204</v>
       </c>
       <c r="B22" s="2" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="29" t="s">
-        <v>197</v>
+      <c r="A23" s="31" t="s">
+        <v>205</v>
       </c>
       <c r="B23" s="2" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="29" t="s">
-        <v>198</v>
+      <c r="A24" s="31" t="s">
+        <v>206</v>
       </c>
       <c r="B24" s="2" t="n">
         <v>6</v>
@@ -3671,20 +3756,20 @@
     </row>
     <row r="25" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="2" t="s">
-        <v>199</v>
+        <v>207</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>200</v>
+        <v>208</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="2" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="2" t="s">
-        <v>202</v>
+        <v>210</v>
       </c>
     </row>
     <row r="1048573" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -3720,45 +3805,45 @@
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>203</v>
+        <v>211</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>204</v>
+        <v>212</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="C2" s="30" t="n">
+        <v>213</v>
+      </c>
+      <c r="C2" s="32" t="n">
         <v>0.3</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>206</v>
+        <v>214</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="C3" s="30" t="n">
+        <v>215</v>
+      </c>
+      <c r="C3" s="32" t="n">
         <v>0.5</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>208</v>
+        <v>216</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="C4" s="30" t="n">
+        <v>50</v>
+      </c>
+      <c r="C4" s="32" t="n">
         <v>0.2</v>
       </c>
     </row>

--- a/assets/card_data.xlsx
+++ b/assets/card_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\cpyh\godot\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF9B1663-0E17-48E8-B9CA-87EAC8531AC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90759C4A-0E9B-4330-923D-EAAF82A6AFDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-12960" yWindow="1570" windowWidth="11110" windowHeight="11180" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-21710" yWindow="-110" windowWidth="21820" windowHeight="13900" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="人物" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="400" uniqueCount="270">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="409" uniqueCount="279">
   <si>
     <t>name</t>
   </si>
@@ -460,9 +460,6 @@
     <t>全体敌人</t>
   </si>
   <si>
-    <t xml:space="preserve">千人楔 </t>
-  </si>
-  <si>
     <t>嵌入身体可以获得一千个人的力量</t>
   </si>
   <si>
@@ -1025,6 +1022,46 @@
   </si>
   <si>
     <t>意识</t>
+    <phoneticPr fontId="16" type="noConversion"/>
+  </si>
+  <si>
+    <t>①添加额外属性，在探索时检查，如钓鱼竿，望远镜，心之罗盘</t>
+    <phoneticPr fontId="16" type="noConversion"/>
+  </si>
+  <si>
+    <t>②强化数值，千人这类，身体强化，一次性的，添加数值，没必要取下来</t>
+    <phoneticPr fontId="16" type="noConversion"/>
+  </si>
+  <si>
+    <t>④添加战斗时双方效果，黑暗灯，诅咒针</t>
+    <phoneticPr fontId="16" type="noConversion"/>
+  </si>
+  <si>
+    <t>堆叠</t>
+    <phoneticPr fontId="16" type="noConversion"/>
+  </si>
+  <si>
+    <t>装备背包</t>
+    <phoneticPr fontId="16" type="noConversion"/>
+  </si>
+  <si>
+    <t>装备左右手</t>
+    <phoneticPr fontId="16" type="noConversion"/>
+  </si>
+  <si>
+    <t>也属于装备-》</t>
+    <phoneticPr fontId="16" type="noConversion"/>
+  </si>
+  <si>
+    <t>道具-》</t>
+    <phoneticPr fontId="16" type="noConversion"/>
+  </si>
+  <si>
+    <t>特殊卡片，和人堆叠产生不同效果</t>
+    <phoneticPr fontId="16" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">千人楔 </t>
     <phoneticPr fontId="16" type="noConversion"/>
   </si>
 </sst>
@@ -1255,11 +1292,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1346,6 +1380,12 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1610,31 +1650,31 @@
   <dimension ref="A1:U15"/>
   <sheetFormatPr defaultColWidth="10" defaultRowHeight="14.25" customHeight="1"/>
   <cols>
-    <col min="1" max="3" width="10" style="2"/>
-    <col min="4" max="4" width="4.5" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="4.5" style="2" customWidth="1"/>
-    <col min="6" max="6" width="11" style="2" customWidth="1"/>
-    <col min="14" max="15" width="10" style="2"/>
-    <col min="21" max="21" width="24.75" style="2" customWidth="1"/>
+    <col min="1" max="3" width="10" style="1"/>
+    <col min="4" max="4" width="4.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="4.5" style="1" customWidth="1"/>
+    <col min="6" max="6" width="11" style="1" customWidth="1"/>
+    <col min="14" max="15" width="10" style="1"/>
+    <col min="21" max="21" width="24.75" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:21">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="7" t="s">
-        <v>269</v>
-      </c>
-      <c r="F1" s="2" t="s">
+      <c r="E1" s="6" t="s">
+        <v>268</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
       <c r="G1" t="s">
@@ -1658,156 +1698,156 @@
       <c r="M1" t="s">
         <v>11</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="N1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="O1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="U1" s="2" t="s">
+      <c r="U1" s="1" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="2" spans="1:21" ht="94.5">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B2" s="2">
+      <c r="B2" s="1">
         <v>10</v>
       </c>
-      <c r="C2" s="2">
+      <c r="C2" s="1">
         <v>1</v>
       </c>
-      <c r="D2" s="2">
+      <c r="D2" s="1">
         <v>0</v>
       </c>
-      <c r="E2" s="2">
+      <c r="E2" s="1">
         <v>80</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="G2" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="H2" s="3" t="s">
+      <c r="H2" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="N2" s="2" t="s">
+      <c r="N2" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="U2" s="4" t="s">
+      <c r="U2" s="3" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="3" spans="1:21" ht="81">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B3" s="2">
+      <c r="B3" s="1">
         <v>50</v>
       </c>
-      <c r="C3" s="2">
+      <c r="C3" s="1">
         <v>5</v>
       </c>
-      <c r="D3" s="2">
+      <c r="D3" s="1">
         <v>50</v>
       </c>
-      <c r="E3" s="2">
+      <c r="E3" s="1">
         <v>20</v>
       </c>
-      <c r="N3" s="2" t="s">
+      <c r="N3" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="U3" s="4" t="s">
+      <c r="U3" s="3" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="4" spans="1:21">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B4" s="2">
+      <c r="B4" s="1">
         <v>30</v>
       </c>
-      <c r="C4" s="2">
+      <c r="C4" s="1">
         <v>8</v>
       </c>
-      <c r="D4" s="2">
+      <c r="D4" s="1">
         <v>5</v>
       </c>
-      <c r="E4" s="2">
+      <c r="E4" s="1">
         <v>100</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="F4" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="N4" s="2" t="s">
+      <c r="N4" s="1" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="7" spans="1:21" ht="14.25" customHeight="1">
-      <c r="A7" s="7" t="s">
+      <c r="A7" s="6" t="s">
+        <v>258</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>264</v>
+      </c>
+      <c r="F7" s="6"/>
+    </row>
+    <row r="8" spans="1:21" ht="14.25" customHeight="1">
+      <c r="A8" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B8" s="6" t="s">
         <v>259</v>
       </c>
-      <c r="B7" s="7" t="s">
+    </row>
+    <row r="9" spans="1:21" ht="14.25" customHeight="1">
+      <c r="A9" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" ht="14.25" customHeight="1">
+      <c r="A10" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" ht="14.25" customHeight="1">
+      <c r="A11" s="35" t="s">
+        <v>29</v>
+      </c>
+      <c r="B11" s="36" t="s">
+        <v>261</v>
+      </c>
+      <c r="C11" s="35"/>
+      <c r="G11" s="38" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="12" spans="1:21" ht="14.25" customHeight="1">
+      <c r="A12" s="37" t="s">
+        <v>260</v>
+      </c>
+      <c r="B12" s="35"/>
+      <c r="C12" s="35"/>
+    </row>
+    <row r="13" spans="1:21" ht="14.25" customHeight="1">
+      <c r="A13" s="6" t="s">
         <v>265</v>
       </c>
-      <c r="F7" s="7"/>
-    </row>
-    <row r="8" spans="1:21" ht="14.25" customHeight="1">
-      <c r="A8" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="B8" s="7" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="9" spans="1:21" ht="14.25" customHeight="1">
-      <c r="A9" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="B9" s="7" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="10" spans="1:21" ht="14.25" customHeight="1">
-      <c r="A10" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="B10" s="7" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="11" spans="1:21" ht="14.25" customHeight="1">
-      <c r="A11" s="36" t="s">
-        <v>29</v>
-      </c>
-      <c r="B11" s="37" t="s">
-        <v>262</v>
-      </c>
-      <c r="C11" s="36"/>
-      <c r="G11" s="39" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="12" spans="1:21" ht="14.25" customHeight="1">
-      <c r="A12" s="38" t="s">
-        <v>261</v>
-      </c>
-      <c r="B12" s="36"/>
-      <c r="C12" s="36"/>
-    </row>
-    <row r="13" spans="1:21" ht="14.25" customHeight="1">
-      <c r="A13" s="7" t="s">
+      <c r="B13" s="6" t="s">
         <v>266</v>
       </c>
-      <c r="B13" s="7" t="s">
-        <v>267</v>
-      </c>
     </row>
     <row r="14" spans="1:21" ht="14.25" customHeight="1">
-      <c r="A14" s="7"/>
+      <c r="A14" s="6"/>
     </row>
     <row r="15" spans="1:21" ht="14.25" customHeight="1">
-      <c r="A15" s="7"/>
+      <c r="A15" s="6"/>
     </row>
   </sheetData>
   <phoneticPr fontId="16" type="noConversion"/>
@@ -1834,51 +1874,51 @@
         <v>30</v>
       </c>
       <c r="B1" t="s">
+        <v>213</v>
+      </c>
+      <c r="C1" t="s">
         <v>214</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>215</v>
       </c>
-      <c r="D1" t="s">
+      <c r="F1" t="s">
         <v>216</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="J1" t="s">
         <v>217</v>
       </c>
-      <c r="G1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="J1" t="s">
+      <c r="M1" s="26" t="s">
         <v>218</v>
       </c>
-      <c r="M1" s="27" t="s">
+    </row>
+    <row r="2" spans="1:13" ht="14.25">
+      <c r="A2" s="31" t="s">
         <v>219</v>
       </c>
-    </row>
-    <row r="2" spans="1:13" ht="14.25">
-      <c r="A2" s="32" t="s">
+      <c r="B2" t="s">
         <v>220</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>221</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>222</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>223</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>224</v>
-      </c>
-      <c r="F2" t="s">
-        <v>225</v>
       </c>
       <c r="G2">
         <v>30</v>
@@ -1891,136 +1931,136 @@
       </c>
     </row>
     <row r="3" spans="1:13" ht="14.25">
-      <c r="A3" s="33" t="s">
+      <c r="A3" s="32" t="s">
+        <v>225</v>
+      </c>
+      <c r="B3" t="s">
         <v>226</v>
       </c>
-      <c r="B3" t="s">
+      <c r="D3" t="s">
         <v>227</v>
       </c>
-      <c r="D3" t="s">
+    </row>
+    <row r="4" spans="1:13" ht="14.25">
+      <c r="A4" s="10" t="s">
         <v>228</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="14.25">
-      <c r="A4" s="11" t="s">
+      <c r="B4" t="s">
         <v>229</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
         <v>230</v>
       </c>
-      <c r="C4" t="s">
+      <c r="F4" t="s">
         <v>231</v>
       </c>
-      <c r="F4" t="s">
+      <c r="J4" t="s">
         <v>232</v>
       </c>
-      <c r="J4" t="s">
+    </row>
+    <row r="5" spans="1:13" ht="14.25">
+      <c r="A5" s="33" t="s">
         <v>233</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="14.25">
-      <c r="A5" s="34" t="s">
+      <c r="B5" t="s">
         <v>234</v>
       </c>
-      <c r="B5" t="s">
+    </row>
+    <row r="6" spans="1:13" ht="14.25">
+      <c r="A6" s="33" t="s">
         <v>235</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" ht="14.25">
-      <c r="A6" s="34" t="s">
+      <c r="B6" t="s">
+        <v>229</v>
+      </c>
+      <c r="C6" t="s">
         <v>236</v>
       </c>
-      <c r="B6" t="s">
+      <c r="F6" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" ht="14.25">
+      <c r="A7" s="34" t="s">
+        <v>238</v>
+      </c>
+      <c r="B7" t="s">
+        <v>239</v>
+      </c>
+      <c r="C7" t="s">
         <v>230</v>
       </c>
-      <c r="C6" t="s">
-        <v>237</v>
-      </c>
-      <c r="F6" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" ht="14.25">
-      <c r="A7" s="35" t="s">
-        <v>239</v>
-      </c>
-      <c r="B7" t="s">
+      <c r="D7" t="s">
         <v>240</v>
       </c>
-      <c r="C7" t="s">
-        <v>231</v>
-      </c>
-      <c r="D7" t="s">
+    </row>
+    <row r="8" spans="1:13" ht="14.25">
+      <c r="A8" s="33" t="s">
         <v>241</v>
       </c>
-    </row>
-    <row r="8" spans="1:13" ht="14.25">
-      <c r="A8" s="34" t="s">
+      <c r="B8" t="s">
         <v>242</v>
       </c>
-      <c r="B8" t="s">
+      <c r="C8" t="s">
         <v>243</v>
       </c>
-      <c r="C8" t="s">
+      <c r="D8" t="s">
         <v>244</v>
       </c>
-      <c r="D8" t="s">
+      <c r="F8" t="s">
         <v>245</v>
       </c>
-      <c r="F8" t="s">
+    </row>
+    <row r="9" spans="1:13" ht="14.25">
+      <c r="A9" s="10" t="s">
         <v>246</v>
       </c>
-    </row>
-    <row r="9" spans="1:13" ht="14.25">
-      <c r="A9" s="11" t="s">
-        <v>247</v>
-      </c>
       <c r="B9" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="D9" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="10" spans="1:13" ht="14.25">
-      <c r="A10" s="33" t="s">
+      <c r="A10" s="32" t="s">
+        <v>247</v>
+      </c>
+      <c r="D10" t="s">
         <v>248</v>
       </c>
-      <c r="D10" t="s">
+    </row>
+    <row r="11" spans="1:13" ht="28.5">
+      <c r="A11" s="33" t="s">
         <v>249</v>
       </c>
-    </row>
-    <row r="11" spans="1:13" ht="28.5">
-      <c r="A11" s="34" t="s">
+      <c r="B11" t="s">
         <v>250</v>
       </c>
-      <c r="B11" t="s">
+      <c r="C11" t="s">
         <v>251</v>
       </c>
-      <c r="C11" t="s">
+      <c r="F11" t="s">
         <v>252</v>
       </c>
-      <c r="F11" t="s">
+    </row>
+    <row r="12" spans="1:13" ht="14.25">
+      <c r="A12" s="33" t="s">
         <v>253</v>
       </c>
-    </row>
-    <row r="12" spans="1:13" ht="14.25">
-      <c r="A12" s="34" t="s">
+      <c r="B12" t="s">
         <v>254</v>
       </c>
-      <c r="B12" t="s">
+      <c r="F12" t="s">
         <v>255</v>
       </c>
-      <c r="F12" t="s">
+    </row>
+    <row r="13" spans="1:13" ht="14.25">
+      <c r="A13" s="10" t="s">
         <v>256</v>
       </c>
-    </row>
-    <row r="13" spans="1:13" ht="14.25">
-      <c r="A13" s="11" t="s">
+      <c r="D13" t="s">
         <v>257</v>
-      </c>
-      <c r="D13" t="s">
-        <v>258</v>
       </c>
     </row>
   </sheetData>
@@ -2039,386 +2079,386 @@
   <dimension ref="A1:J13"/>
   <sheetFormatPr defaultColWidth="10" defaultRowHeight="14.25" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="8.875" style="2" customWidth="1"/>
-    <col min="2" max="2" width="5.125" style="2" customWidth="1"/>
-    <col min="3" max="3" width="5.375" style="2" customWidth="1"/>
-    <col min="4" max="4" width="6.375" style="2" customWidth="1"/>
-    <col min="5" max="5" width="19.75" style="2" customWidth="1"/>
-    <col min="6" max="6" width="14.125" style="2" customWidth="1"/>
-    <col min="7" max="8" width="6.375" style="2" customWidth="1"/>
-    <col min="9" max="9" width="10.875" style="2" customWidth="1"/>
-    <col min="10" max="10" width="30.375" style="2" customWidth="1"/>
+    <col min="1" max="1" width="8.875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="5.125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="5.375" style="1" customWidth="1"/>
+    <col min="4" max="4" width="6.375" style="1" customWidth="1"/>
+    <col min="5" max="5" width="19.75" style="1" customWidth="1"/>
+    <col min="6" max="6" width="14.125" style="1" customWidth="1"/>
+    <col min="7" max="8" width="6.375" style="1" customWidth="1"/>
+    <col min="9" max="9" width="10.875" style="1" customWidth="1"/>
+    <col min="10" max="10" width="30.375" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="1" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="2" spans="1:10">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="C2" s="2">
+      <c r="C2" s="1">
         <v>1</v>
       </c>
-      <c r="D2" s="2">
+      <c r="D2" s="1">
         <v>0</v>
       </c>
-      <c r="G2" s="2">
+      <c r="G2" s="1">
         <v>1</v>
       </c>
-      <c r="H2" s="2">
+      <c r="H2" s="1">
         <v>1</v>
       </c>
-      <c r="I2" s="2" t="b">
+      <c r="I2" s="1" t="b">
         <f>FALSE()</f>
         <v>0</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="J2" s="1" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="3" spans="1:10">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="C3" s="2">
+      <c r="C3" s="1">
         <v>1</v>
       </c>
-      <c r="D3" s="2">
+      <c r="D3" s="1">
         <v>0</v>
       </c>
-      <c r="G3" s="2">
+      <c r="G3" s="1">
         <v>2</v>
       </c>
-      <c r="H3" s="2">
+      <c r="H3" s="1">
         <v>1</v>
       </c>
-      <c r="I3" s="2" t="b">
+      <c r="I3" s="1" t="b">
         <f>FALSE()</f>
         <v>0</v>
       </c>
-      <c r="J3" s="2" t="s">
+      <c r="J3" s="1" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="4" spans="1:10">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="C4" s="2">
+      <c r="C4" s="1">
         <v>0</v>
       </c>
-      <c r="D4" s="2">
+      <c r="D4" s="1">
         <v>0</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="E4" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="G4" s="2">
+      <c r="G4" s="1">
         <v>3</v>
       </c>
-      <c r="H4" s="2">
+      <c r="H4" s="1">
         <v>2</v>
       </c>
-      <c r="I4" s="2" t="b">
+      <c r="I4" s="1" t="b">
         <f>FALSE()</f>
         <v>0</v>
       </c>
-      <c r="J4" s="2" t="s">
+      <c r="J4" s="1" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="5" spans="1:10">
-      <c r="A5" s="2" t="s">
+      <c r="A5" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="C5" s="2">
+      <c r="C5" s="1">
         <v>0</v>
       </c>
-      <c r="D5" s="2">
+      <c r="D5" s="1">
         <v>0</v>
       </c>
-      <c r="G5" s="2">
+      <c r="G5" s="1">
         <v>4</v>
       </c>
-      <c r="H5" s="2">
+      <c r="H5" s="1">
         <v>3</v>
       </c>
-      <c r="I5" s="2" t="b">
+      <c r="I5" s="1" t="b">
         <f>FALSE()</f>
         <v>0</v>
       </c>
-      <c r="J5" s="2" t="s">
+      <c r="J5" s="1" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="6" spans="1:10">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="C6" s="2">
+      <c r="C6" s="1">
         <v>0</v>
       </c>
-      <c r="D6" s="2">
+      <c r="D6" s="1">
         <v>2</v>
       </c>
-      <c r="G6" s="2">
+      <c r="G6" s="1">
         <v>5</v>
       </c>
-      <c r="H6" s="2">
+      <c r="H6" s="1">
         <v>0</v>
       </c>
-      <c r="I6" s="2" t="b">
+      <c r="I6" s="1" t="b">
         <f>FALSE()</f>
         <v>0</v>
       </c>
-      <c r="J6" s="2" t="s">
+      <c r="J6" s="1" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="7" spans="1:10">
-      <c r="A7" s="2" t="s">
+      <c r="A7" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="C7" s="2">
+      <c r="C7" s="1">
         <v>2</v>
       </c>
-      <c r="D7" s="2">
+      <c r="D7" s="1">
         <v>0</v>
       </c>
-      <c r="F7" s="2" t="s">
+      <c r="F7" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="G7" s="2">
+      <c r="G7" s="1">
         <v>6</v>
       </c>
-      <c r="H7" s="2">
+      <c r="H7" s="1">
         <v>5</v>
       </c>
-      <c r="I7" s="2" t="b">
+      <c r="I7" s="1" t="b">
         <f>FALSE()</f>
         <v>0</v>
       </c>
-      <c r="J7" s="2" t="s">
+      <c r="J7" s="1" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="8" spans="1:10">
-      <c r="A8" s="2" t="s">
+      <c r="A8" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="C8" s="2">
+      <c r="C8" s="1">
         <v>2</v>
       </c>
-      <c r="D8" s="2">
+      <c r="D8" s="1">
         <v>0</v>
       </c>
-      <c r="F8" s="2" t="s">
+      <c r="F8" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="G8" s="2">
+      <c r="G8" s="1">
         <v>7</v>
       </c>
-      <c r="H8" s="2">
+      <c r="H8" s="1">
         <v>5</v>
       </c>
-      <c r="I8" s="2" t="b">
+      <c r="I8" s="1" t="b">
         <f>FALSE()</f>
         <v>0</v>
       </c>
-      <c r="J8" s="2" t="s">
+      <c r="J8" s="1" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="9" spans="1:10">
-      <c r="A9" s="2" t="s">
+      <c r="A9" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B9" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="C9" s="2">
+      <c r="C9" s="1">
         <v>6</v>
       </c>
-      <c r="D9" s="2">
+      <c r="D9" s="1">
         <v>1</v>
       </c>
-      <c r="F9" s="7" t="s">
+      <c r="F9" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="G9" s="2">
+      <c r="G9" s="1">
         <v>8</v>
       </c>
-      <c r="H9" s="2">
+      <c r="H9" s="1">
         <v>10</v>
       </c>
-      <c r="I9" s="2" t="b">
+      <c r="I9" s="1" t="b">
         <f>FALSE()</f>
         <v>0</v>
       </c>
-      <c r="J9" s="2" t="s">
+      <c r="J9" s="1" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="10" spans="1:10">
-      <c r="A10" s="2" t="s">
+      <c r="A10" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B10" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="C10" s="2">
+      <c r="C10" s="1">
         <v>3</v>
       </c>
-      <c r="D10" s="2">
+      <c r="D10" s="1">
         <v>2</v>
       </c>
-      <c r="F10" s="7" t="s">
+      <c r="F10" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="G10" s="2">
+      <c r="G10" s="1">
         <v>9</v>
       </c>
-      <c r="H10" s="2">
+      <c r="H10" s="1">
         <v>5</v>
       </c>
-      <c r="I10" s="2" t="b">
+      <c r="I10" s="1" t="b">
         <f>FALSE()</f>
         <v>0</v>
       </c>
-      <c r="J10" s="2" t="s">
+      <c r="J10" s="1" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="11" spans="1:10">
-      <c r="A11" s="2" t="s">
+      <c r="A11" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B11" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="C11" s="2">
+      <c r="C11" s="1">
         <v>0</v>
       </c>
-      <c r="D11" s="2">
+      <c r="D11" s="1">
         <v>2</v>
       </c>
-      <c r="G11" s="2">
+      <c r="G11" s="1">
         <v>10</v>
       </c>
-      <c r="H11" s="2">
+      <c r="H11" s="1">
         <v>0</v>
       </c>
-      <c r="I11" s="2" t="b">
+      <c r="I11" s="1" t="b">
         <f>FALSE()</f>
         <v>0</v>
       </c>
-      <c r="J11" s="2" t="s">
+      <c r="J11" s="1" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="12" spans="1:10">
-      <c r="A12" s="7" t="s">
+      <c r="A12" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="B12" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="C12" s="2">
+      <c r="C12" s="1">
         <v>0</v>
       </c>
-      <c r="D12" s="2">
+      <c r="D12" s="1">
         <v>0</v>
       </c>
-      <c r="E12" s="3"/>
-      <c r="G12" s="2">
+      <c r="E12" s="2"/>
+      <c r="G12" s="1">
         <v>11</v>
       </c>
-      <c r="H12" s="2">
+      <c r="H12" s="1">
         <v>100</v>
       </c>
-      <c r="I12" s="2" t="b">
+      <c r="I12" s="1" t="b">
         <f>TRUE()</f>
         <v>1</v>
       </c>
-      <c r="J12" s="2" t="s">
+      <c r="J12" s="1" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="13" spans="1:10">
-      <c r="A13" s="8" t="s">
+      <c r="A13" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B13" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C13" s="2">
+      <c r="C13" s="1">
         <v>0</v>
       </c>
-      <c r="D13" s="2">
+      <c r="D13" s="1">
         <v>0</v>
       </c>
-      <c r="G13" s="2">
+      <c r="G13" s="1">
         <v>12</v>
       </c>
-      <c r="H13" s="2">
+      <c r="H13" s="1">
         <v>20</v>
       </c>
-      <c r="I13" s="2" t="b">
+      <c r="I13" s="1" t="b">
         <f>FALSE()</f>
         <v>0</v>
       </c>
-      <c r="J13" s="2" t="s">
+      <c r="J13" s="1" t="s">
         <v>47</v>
       </c>
     </row>
@@ -2434,21 +2474,21 @@
   <dimension ref="A1:H13"/>
   <sheetFormatPr defaultColWidth="10" defaultRowHeight="14.25" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="14.125" style="2" customWidth="1"/>
-    <col min="2" max="3" width="10" style="2"/>
+    <col min="1" max="1" width="14.125" style="1" customWidth="1"/>
+    <col min="2" max="3" width="10" style="1"/>
     <col min="5" max="5" width="30.25" customWidth="1"/>
-    <col min="6" max="7" width="10" style="2"/>
-    <col min="8" max="8" width="6.625" style="2" customWidth="1"/>
+    <col min="6" max="7" width="10" style="1"/>
+    <col min="8" max="8" width="6.625" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D1" t="s">
@@ -2457,93 +2497,93 @@
       <c r="E1" t="s">
         <v>35</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="1" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="2" spans="1:8">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="1" t="s">
         <v>62</v>
       </c>
       <c r="D2">
         <v>13</v>
       </c>
-      <c r="F2" s="2">
+      <c r="F2" s="1">
         <v>5</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="G2" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="H2" s="1" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="3" spans="1:8">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="1" t="s">
         <v>67</v>
       </c>
       <c r="D3">
         <v>14</v>
       </c>
-      <c r="F3" s="2">
+      <c r="F3" s="1">
         <v>6</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="G3" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="H3" s="1" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="4" spans="1:8">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="1" t="s">
         <v>70</v>
       </c>
       <c r="D4">
         <v>15</v>
       </c>
-      <c r="F4" s="2">
+      <c r="F4" s="1">
         <v>7</v>
       </c>
-      <c r="G4" s="2" t="s">
+      <c r="G4" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="H4" s="2" t="s">
+      <c r="H4" s="1" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="5" spans="1:8">
-      <c r="A5" s="7" t="s">
+      <c r="A5" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="1" t="s">
         <v>71</v>
       </c>
       <c r="D5">
@@ -2552,24 +2592,24 @@
       <c r="E5" t="s">
         <v>72</v>
       </c>
-      <c r="F5" s="2">
+      <c r="F5" s="1">
         <v>8</v>
       </c>
-      <c r="G5" s="2" t="s">
+      <c r="G5" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="H5" s="2" t="s">
+      <c r="H5" s="1" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="6" spans="1:8">
-      <c r="A6" s="2" t="s">
+      <c r="A6" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="1" t="s">
         <v>74</v>
       </c>
       <c r="D6">
@@ -2578,188 +2618,188 @@
       <c r="E6" t="s">
         <v>75</v>
       </c>
-      <c r="F6" s="2">
+      <c r="F6" s="1">
         <v>90</v>
       </c>
-      <c r="G6" s="2" t="s">
+      <c r="G6" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="H6" s="2" t="s">
+      <c r="H6" s="1" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="7" spans="1:8">
-      <c r="A7" s="2" t="s">
+      <c r="A7" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C7" s="1" t="s">
         <v>77</v>
       </c>
       <c r="D7">
         <v>18</v>
       </c>
-      <c r="F7" s="2">
+      <c r="F7" s="1">
         <v>10</v>
       </c>
-      <c r="G7" s="2" t="s">
+      <c r="G7" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="H7" s="2" t="s">
+      <c r="H7" s="1" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="8" spans="1:8">
-      <c r="A8" s="2" t="s">
+      <c r="A8" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="C8" s="1" t="s">
         <v>79</v>
       </c>
       <c r="D8">
         <v>20</v>
       </c>
-      <c r="F8" s="2">
+      <c r="F8" s="1">
         <v>1</v>
       </c>
-      <c r="G8" s="2" t="s">
+      <c r="G8" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="H8" s="2" t="s">
+      <c r="H8" s="1" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="9" spans="1:8">
-      <c r="A9" s="2" t="s">
+      <c r="A9" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B9" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="C9" s="1" t="s">
         <v>81</v>
       </c>
       <c r="D9">
         <v>21</v>
       </c>
-      <c r="E9" s="9" t="s">
+      <c r="E9" s="8" t="s">
         <v>82</v>
       </c>
-      <c r="F9" s="2">
+      <c r="F9" s="1">
         <v>150</v>
       </c>
-      <c r="G9" s="2" t="b">
+      <c r="G9" s="1" t="b">
         <f>TRUE()</f>
         <v>1</v>
       </c>
-      <c r="H9" s="2" t="s">
+      <c r="H9" s="1" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="14.25" customHeight="1">
-      <c r="A10" s="9" t="s">
+      <c r="A10" s="8" t="s">
         <v>83</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B10" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="C10" s="1" t="s">
         <v>84</v>
       </c>
       <c r="D10">
         <v>22</v>
       </c>
-      <c r="E10" s="10" t="s">
+      <c r="E10" s="9" t="s">
         <v>85</v>
       </c>
-      <c r="F10" s="2">
+      <c r="F10" s="1">
         <v>100</v>
       </c>
-      <c r="G10" s="2" t="s">
+      <c r="G10" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="H10" s="2" t="s">
+      <c r="H10" s="1" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="14.25" customHeight="1">
-      <c r="A11" s="9" t="s">
+      <c r="A11" s="8" t="s">
         <v>86</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B11" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="C11" s="1" t="s">
         <v>87</v>
       </c>
       <c r="D11">
         <v>23</v>
       </c>
-      <c r="E11" s="10" t="s">
+      <c r="E11" s="9" t="s">
         <v>88</v>
       </c>
-      <c r="F11" s="2">
+      <c r="F11" s="1">
         <v>200</v>
       </c>
-      <c r="G11" s="2" t="s">
+      <c r="G11" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="H11" s="2" t="s">
+      <c r="H11" s="1" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="12" spans="1:8">
-      <c r="A12" s="2" t="s">
+      <c r="A12" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="B12" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="C12" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D12">
         <v>24</v>
       </c>
-      <c r="E12" s="9" t="s">
+      <c r="E12" s="8" t="s">
         <v>91</v>
       </c>
-      <c r="F12" s="2">
+      <c r="F12" s="1">
         <v>60</v>
       </c>
-      <c r="G12" s="2" t="s">
+      <c r="G12" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="H12" s="2" t="s">
+      <c r="H12" s="1" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="13" spans="1:8">
-      <c r="A13" s="2" t="s">
+      <c r="A13" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="B13" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="C13" s="1" t="s">
         <v>93</v>
       </c>
       <c r="D13">
         <v>25</v>
       </c>
-      <c r="F13" s="2">
+      <c r="F13" s="1">
         <v>120</v>
       </c>
-      <c r="G13" s="2" t="b">
+      <c r="G13" s="1" t="b">
         <f>TRUE()</f>
         <v>1</v>
       </c>
-      <c r="H13" s="2" t="s">
+      <c r="H13" s="1" t="s">
         <v>64</v>
       </c>
     </row>
@@ -2775,33 +2815,33 @@
   <dimension ref="A1:J1048576"/>
   <sheetFormatPr defaultColWidth="10" defaultRowHeight="14.25" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="13" style="2" customWidth="1"/>
-    <col min="2" max="2" width="20" style="2" customWidth="1"/>
-    <col min="3" max="3" width="10" style="2"/>
-    <col min="4" max="4" width="11.875" style="2" customWidth="1"/>
-    <col min="5" max="6" width="10" style="2"/>
+    <col min="1" max="1" width="13" style="1" customWidth="1"/>
+    <col min="2" max="2" width="20" style="1" customWidth="1"/>
+    <col min="3" max="3" width="10" style="1"/>
+    <col min="4" max="4" width="11.875" style="1" customWidth="1"/>
+    <col min="5" max="6" width="10" style="1"/>
     <col min="7" max="7" width="25.875" customWidth="1"/>
     <col min="9" max="9" width="17.75" customWidth="1"/>
     <col min="16377" max="16384" width="11" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>12</v>
       </c>
       <c r="G1" t="s">
@@ -2818,19 +2858,19 @@
       </c>
     </row>
     <row r="2" spans="1:10">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="E2" s="2">
+      <c r="E2" s="1">
         <v>1</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="1" t="s">
         <v>47</v>
       </c>
       <c r="G2" t="s">
@@ -2838,20 +2878,20 @@
       </c>
     </row>
     <row r="3" spans="1:10">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="D3" s="2" t="b">
+      <c r="D3" s="1" t="b">
         <f>TRUE()</f>
         <v>1</v>
       </c>
-      <c r="E3" s="2">
+      <c r="E3" s="1">
         <v>200</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F3" s="1" t="s">
         <v>47</v>
       </c>
       <c r="H3" t="s">
@@ -2865,105 +2905,141 @@
       </c>
     </row>
     <row r="4" spans="1:10">
-      <c r="A4" s="11" t="s">
+      <c r="A4" s="40" t="s">
+        <v>278</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="D4" s="2" t="b">
+      <c r="D4" s="1" t="b">
         <f>TRUE()</f>
         <v>1</v>
       </c>
-      <c r="E4" s="2">
+      <c r="E4" s="1">
         <v>100</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="F4" s="1" t="s">
         <v>47</v>
       </c>
       <c r="G4" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="14.25" customHeight="1">
+      <c r="A5" s="1" t="s">
         <v>110</v>
       </c>
-    </row>
-    <row r="5" spans="1:10" ht="14.25" customHeight="1">
-      <c r="A5" s="2" t="s">
+      <c r="B5" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="D5" s="2" t="b">
+      <c r="D5" s="1" t="b">
         <f>TRUE()</f>
         <v>1</v>
       </c>
-      <c r="E5" s="2">
+      <c r="E5" s="1">
         <v>1</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="F5" s="1" t="s">
         <v>47</v>
       </c>
       <c r="H5" t="s">
         <v>105</v>
       </c>
       <c r="I5" t="s">
+        <v>112</v>
+      </c>
+      <c r="J5" t="s">
         <v>113</v>
       </c>
-      <c r="J5" t="s">
+    </row>
+    <row r="6" spans="1:10" ht="14.25" customHeight="1">
+      <c r="A6" s="1" t="s">
         <v>114</v>
       </c>
-    </row>
-    <row r="6" spans="1:10" ht="14.25" customHeight="1">
-      <c r="A6" s="2" t="s">
+      <c r="B6" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="B6" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="D6" s="2" t="b">
+      <c r="D6" s="1" t="b">
         <f>TRUE()</f>
         <v>1</v>
       </c>
-      <c r="E6" s="2">
+      <c r="E6" s="1">
         <v>100</v>
       </c>
-      <c r="F6" s="2" t="s">
+      <c r="F6" s="1" t="s">
         <v>47</v>
       </c>
       <c r="H6" t="s">
         <v>105</v>
       </c>
       <c r="I6" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="J6" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="14.25" customHeight="1">
-      <c r="A7" s="2" t="s">
+      <c r="A7" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="B7" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="D7" s="2" t="b">
+      <c r="D7" s="1" t="b">
         <f>TRUE()</f>
         <v>1</v>
       </c>
-      <c r="E7" s="2">
+      <c r="E7" s="1">
         <v>100</v>
       </c>
-      <c r="F7" s="2" t="s">
+      <c r="F7" s="1" t="s">
         <v>47</v>
       </c>
       <c r="H7">
         <v>1</v>
       </c>
       <c r="I7" t="s">
+        <v>119</v>
+      </c>
+      <c r="J7" t="s">
         <v>120</v>
       </c>
-      <c r="J7" t="s">
-        <v>121</v>
+    </row>
+    <row r="10" spans="1:10" ht="14.25" customHeight="1">
+      <c r="B10" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>273</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="14.25" customHeight="1">
+      <c r="B11" s="6" t="s">
+        <v>277</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>272</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="14.25" customHeight="1">
+      <c r="D12" s="6"/>
+    </row>
+    <row r="13" spans="1:10" ht="14.25" customHeight="1">
+      <c r="B13" s="6" t="s">
+        <v>275</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>274</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>271</v>
       </c>
     </row>
     <row r="1048575" ht="12.75" customHeight="1"/>
@@ -2980,138 +3056,138 @@
   <dimension ref="A1:G30"/>
   <sheetFormatPr defaultColWidth="10" defaultRowHeight="14.25" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="13" style="2" customWidth="1"/>
-    <col min="2" max="2" width="10" style="2"/>
-    <col min="3" max="3" width="27.5" style="2" customWidth="1"/>
-    <col min="4" max="5" width="10" style="2"/>
+    <col min="1" max="1" width="13" style="1" customWidth="1"/>
+    <col min="2" max="2" width="10" style="1"/>
+    <col min="3" max="3" width="27.5" style="1" customWidth="1"/>
+    <col min="4" max="5" width="10" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="E1" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="B2" s="1">
+        <v>0</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="E1" s="2" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="B2" s="2">
-        <v>0</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="D2" s="2" t="s">
+      <c r="E2" s="1">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="E2" s="2">
-        <v>20000</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3" s="2" t="s">
+      <c r="B3" s="1">
+        <v>1</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="B3" s="2">
-        <v>1</v>
-      </c>
-      <c r="C3" s="2" t="s">
+      <c r="D3" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="E3" s="1">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="D3" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="E3" s="2">
-        <v>15000</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4" s="2" t="s">
+      <c r="B4" s="1">
+        <v>2</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="B4" s="2">
-        <v>2</v>
-      </c>
-      <c r="C4" s="2" t="s">
+      <c r="D4" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="E4" s="1">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="D4" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="E4" s="2">
-        <v>10000</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
-      <c r="A5" s="2" t="s">
+      <c r="B5" s="1">
+        <v>4</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="B5" s="2">
+      <c r="E5" s="1">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="B6" s="1">
+        <v>5</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="E6" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="B7" s="1">
         <v>4</v>
       </c>
-      <c r="C5" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="E5" s="2">
+      <c r="C7" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="E7" s="1">
         <v>300</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
-      <c r="A6" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="B6" s="2">
-        <v>5</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="E6" s="2">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
-      <c r="A7" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="B7" s="2">
-        <v>4</v>
-      </c>
-      <c r="C7" s="2" t="s">
+    <row r="8" spans="1:5">
+      <c r="A8" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="E7" s="2">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
-      <c r="A8" s="2" t="s">
+      <c r="B8" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="C8" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="C8" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>136</v>
+      <c r="E8" s="1" t="s">
+        <v>135</v>
       </c>
     </row>
     <row r="30" spans="7:7">
-      <c r="G30" s="2"/>
+      <c r="G30" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="16" type="noConversion"/>
@@ -3130,35 +3206,35 @@
         <v>31</v>
       </c>
       <c r="C1" t="s">
+        <v>137</v>
+      </c>
+      <c r="D1" t="s">
         <v>138</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>139</v>
-      </c>
-      <c r="E1" t="s">
-        <v>140</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" t="s">
+        <v>140</v>
+      </c>
+      <c r="B2" t="s">
         <v>141</v>
-      </c>
-      <c r="B2" t="s">
-        <v>142</v>
       </c>
       <c r="C2">
         <v>2</v>
       </c>
       <c r="E2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C3">
         <v>10</v>
@@ -3167,40 +3243,40 @@
         <v>1</v>
       </c>
       <c r="E3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B4" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C4">
         <v>4</v>
       </c>
       <c r="E4" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B5" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C5">
         <v>1000</v>
       </c>
       <c r="E5" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
   </sheetData>
@@ -3223,205 +3299,205 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>36</v>
       </c>
       <c r="C1" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" s="11" t="s">
         <v>150</v>
       </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" s="12" t="s">
+      <c r="B2" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="11" t="s">
         <v>151</v>
       </c>
-      <c r="B2" s="12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" s="12" t="s">
-        <v>152</v>
-      </c>
-      <c r="B3" s="12">
+      <c r="B3" s="11">
         <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:3">
-      <c r="A4" s="12" t="s">
+      <c r="A4" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="B4" s="12">
+      <c r="B4" s="11">
         <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:3">
-      <c r="A5" s="12" t="s">
+      <c r="A5" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="B5" s="12">
+      <c r="B5" s="11">
         <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:3">
-      <c r="A6" s="13" t="s">
+      <c r="A6" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="B6" s="12">
+      <c r="B6" s="11">
         <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:3">
-      <c r="A7" s="12" t="s">
+      <c r="A7" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="B7" s="12">
+      <c r="B7" s="11">
         <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:3">
-      <c r="A8" s="12" t="s">
+      <c r="A8" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="B8" s="12">
+      <c r="B8" s="11">
         <v>7</v>
       </c>
     </row>
     <row r="9" spans="1:3">
-      <c r="A9" s="12" t="s">
+      <c r="A9" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="B9" s="12">
+      <c r="B9" s="11">
         <v>8</v>
       </c>
     </row>
     <row r="10" spans="1:3">
-      <c r="A10" s="12" t="s">
+      <c r="A10" s="11" t="s">
         <v>56</v>
       </c>
-      <c r="B10" s="12">
+      <c r="B10" s="11">
         <v>9</v>
       </c>
     </row>
     <row r="11" spans="1:3">
-      <c r="A11" s="12" t="s">
+      <c r="A11" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="B11" s="12">
+      <c r="B11" s="11">
         <v>10</v>
       </c>
     </row>
     <row r="12" spans="1:3">
-      <c r="A12" s="12" t="s">
-        <v>128</v>
-      </c>
-      <c r="B12" s="12">
+      <c r="A12" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="B12" s="11">
         <v>11</v>
       </c>
     </row>
     <row r="13" spans="1:3">
-      <c r="A13" s="13" t="s">
+      <c r="A13" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="B13" s="12">
+      <c r="B13" s="11">
         <v>12</v>
       </c>
     </row>
     <row r="14" spans="1:3">
-      <c r="A14" s="14" t="s">
+      <c r="A14" s="13" t="s">
         <v>60</v>
       </c>
-      <c r="B14" s="15">
+      <c r="B14" s="14">
         <v>13</v>
       </c>
     </row>
     <row r="15" spans="1:3">
-      <c r="A15" s="14" t="s">
+      <c r="A15" s="13" t="s">
         <v>65</v>
       </c>
-      <c r="B15" s="15">
+      <c r="B15" s="14">
         <v>14</v>
       </c>
     </row>
     <row r="16" spans="1:3">
-      <c r="A16" s="14" t="s">
+      <c r="A16" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="B16" s="15">
+      <c r="B16" s="14">
         <v>15</v>
       </c>
     </row>
     <row r="17" spans="1:2">
-      <c r="A17" s="14" t="s">
+      <c r="A17" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="B17" s="15">
+      <c r="B17" s="14">
         <v>16</v>
       </c>
     </row>
     <row r="18" spans="1:2">
-      <c r="A18" s="14" t="s">
+      <c r="A18" s="13" t="s">
         <v>73</v>
       </c>
-      <c r="B18" s="15">
+      <c r="B18" s="14">
         <v>17</v>
       </c>
     </row>
     <row r="19" spans="1:2">
-      <c r="A19" s="14" t="s">
+      <c r="A19" s="13" t="s">
         <v>76</v>
       </c>
-      <c r="B19" s="15">
+      <c r="B19" s="14">
         <v>18</v>
       </c>
     </row>
     <row r="20" spans="1:2">
-      <c r="A20" s="14" t="s">
+      <c r="A20" s="13" t="s">
         <v>78</v>
       </c>
-      <c r="B20" s="15">
+      <c r="B20" s="14">
         <v>20</v>
       </c>
     </row>
     <row r="21" spans="1:2">
-      <c r="A21" s="14" t="s">
+      <c r="A21" s="13" t="s">
         <v>80</v>
       </c>
-      <c r="B21" s="15">
+      <c r="B21" s="14">
         <v>21</v>
       </c>
     </row>
     <row r="22" spans="1:2">
-      <c r="A22" s="16" t="s">
+      <c r="A22" s="15" t="s">
         <v>83</v>
       </c>
-      <c r="B22" s="15">
+      <c r="B22" s="14">
         <v>22</v>
       </c>
     </row>
     <row r="23" spans="1:2">
-      <c r="A23" s="16" t="s">
+      <c r="A23" s="15" t="s">
         <v>86</v>
       </c>
-      <c r="B23" s="15">
+      <c r="B23" s="14">
         <v>23</v>
       </c>
     </row>
     <row r="24" spans="1:2">
-      <c r="A24" s="14" t="s">
+      <c r="A24" s="13" t="s">
         <v>89</v>
       </c>
-      <c r="B24" s="15">
+      <c r="B24" s="14">
         <v>24</v>
       </c>
     </row>
     <row r="25" spans="1:2">
-      <c r="A25" s="14" t="s">
+      <c r="A25" s="13" t="s">
         <v>92</v>
       </c>
-      <c r="B25" s="15">
+      <c r="B25" s="14">
         <v>25</v>
       </c>
     </row>
@@ -3447,278 +3523,278 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="21">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="39" t="s">
+        <v>152</v>
+      </c>
+      <c r="B1" s="39"/>
+      <c r="C1" s="39"/>
+      <c r="D1" s="39"/>
+      <c r="E1" s="39"/>
+      <c r="F1" s="39"/>
+      <c r="G1" s="39"/>
+    </row>
+    <row r="2" spans="1:7" ht="18">
+      <c r="A2" s="16" t="s">
         <v>153</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-    </row>
-    <row r="2" spans="1:7" ht="18">
-      <c r="A2" s="17" t="s">
+      <c r="B2" s="17" t="s">
         <v>154</v>
       </c>
-      <c r="B2" s="18" t="s">
+      <c r="C2" s="16" t="s">
         <v>155</v>
       </c>
-      <c r="C2" s="17" t="s">
+      <c r="D2" s="16" t="s">
         <v>156</v>
       </c>
-      <c r="D2" s="17" t="s">
+      <c r="E2" s="16" t="s">
         <v>157</v>
       </c>
-      <c r="E2" s="17" t="s">
+      <c r="F2" s="16" t="s">
         <v>158</v>
       </c>
-      <c r="F2" s="17" t="s">
+      <c r="G2" s="17" t="s">
         <v>159</v>
       </c>
-      <c r="G2" s="18" t="s">
+    </row>
+    <row r="3" spans="1:7" ht="33">
+      <c r="A3" s="18" t="s">
         <v>160</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" ht="33">
-      <c r="A3" s="19" t="s">
+      <c r="B3" s="19" t="s">
         <v>161</v>
       </c>
-      <c r="B3" s="20" t="s">
+      <c r="C3" s="18" t="s">
         <v>162</v>
       </c>
-      <c r="C3" s="19" t="s">
+      <c r="D3" s="18" t="s">
         <v>163</v>
       </c>
-      <c r="D3" s="19" t="s">
+      <c r="E3" s="18" t="s">
         <v>164</v>
       </c>
-      <c r="E3" s="19" t="s">
-        <v>165</v>
-      </c>
-      <c r="F3" s="19" t="b">
+      <c r="F3" s="18" t="b">
         <f>FALSE()</f>
         <v>0</v>
       </c>
-      <c r="G3" s="20" t="s">
+      <c r="G3" s="19" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="33">
+      <c r="A4" s="18" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="4" spans="1:7" ht="33">
-      <c r="A4" s="19" t="s">
+      <c r="B4" s="19" t="s">
         <v>167</v>
       </c>
-      <c r="B4" s="20" t="s">
+      <c r="C4" s="18" t="s">
+        <v>166</v>
+      </c>
+      <c r="D4" s="18" t="s">
         <v>168</v>
       </c>
-      <c r="C4" s="19" t="s">
-        <v>167</v>
-      </c>
-      <c r="D4" s="19" t="s">
+      <c r="E4" s="18" t="s">
         <v>169</v>
       </c>
-      <c r="E4" s="19" t="s">
-        <v>170</v>
-      </c>
-      <c r="F4" s="19" t="b">
+      <c r="F4" s="18" t="b">
         <f>TRUE()</f>
         <v>1</v>
       </c>
-      <c r="G4" s="20" t="s">
+      <c r="G4" s="19" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="16.5">
+      <c r="A5" s="18" t="s">
         <v>171</v>
       </c>
-    </row>
-    <row r="5" spans="1:7" ht="16.5">
-      <c r="A5" s="19" t="s">
+      <c r="B5" s="19" t="s">
         <v>172</v>
       </c>
-      <c r="B5" s="20" t="s">
+      <c r="C5" s="18" t="s">
         <v>173</v>
       </c>
-      <c r="C5" s="19" t="s">
+      <c r="D5" s="18" t="s">
         <v>174</v>
       </c>
-      <c r="D5" s="19" t="s">
+      <c r="E5" s="18" t="s">
         <v>175</v>
       </c>
-      <c r="E5" s="19" t="s">
-        <v>176</v>
-      </c>
-      <c r="F5" s="19" t="b">
+      <c r="F5" s="18" t="b">
         <f>TRUE()</f>
         <v>1</v>
       </c>
-      <c r="G5" s="20" t="s">
-        <v>175</v>
+      <c r="G5" s="19" t="s">
+        <v>174</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="16.5">
-      <c r="A6" s="19" t="s">
+      <c r="A6" s="18" t="s">
+        <v>176</v>
+      </c>
+      <c r="B6" s="19" t="s">
         <v>177</v>
       </c>
-      <c r="B6" s="20" t="s">
+      <c r="C6" s="18" t="s">
         <v>178</v>
       </c>
-      <c r="C6" s="19" t="s">
-        <v>179</v>
-      </c>
-      <c r="D6" s="19" t="s">
+      <c r="D6" s="18" t="s">
+        <v>168</v>
+      </c>
+      <c r="E6" s="18" t="s">
         <v>169</v>
       </c>
-      <c r="E6" s="19" t="s">
-        <v>170</v>
-      </c>
-      <c r="F6" s="19" t="b">
+      <c r="F6" s="18" t="b">
         <f>TRUE()</f>
         <v>1</v>
       </c>
-      <c r="G6" s="20" t="s">
-        <v>175</v>
+      <c r="G6" s="19" t="s">
+        <v>174</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="33">
-      <c r="A7" s="19" t="s">
+      <c r="A7" s="18" t="s">
+        <v>179</v>
+      </c>
+      <c r="B7" s="19" t="s">
         <v>180</v>
       </c>
-      <c r="B7" s="20" t="s">
+      <c r="C7" s="18" t="s">
+        <v>162</v>
+      </c>
+      <c r="D7" s="18" t="s">
         <v>181</v>
       </c>
-      <c r="C7" s="19" t="s">
-        <v>163</v>
-      </c>
-      <c r="D7" s="19" t="s">
+      <c r="E7" s="18" t="s">
         <v>182</v>
       </c>
-      <c r="E7" s="19" t="s">
-        <v>183</v>
-      </c>
-      <c r="F7" s="19" t="b">
+      <c r="F7" s="18" t="b">
         <f>FALSE()</f>
         <v>0</v>
       </c>
-      <c r="G7" s="20" t="s">
+      <c r="G7" s="19" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="14.25">
+      <c r="A10" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="C10" s="1"/>
+      <c r="D10" s="1" t="s">
         <v>184</v>
       </c>
-    </row>
-    <row r="10" spans="1:7" ht="14.25">
-      <c r="A10" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2" t="s">
+      <c r="E10" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="E10" s="2" t="s">
+      <c r="F10" s="1">
+        <v>300</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="13.5" customHeight="1">
+      <c r="A11" s="20" t="s">
         <v>186</v>
       </c>
-      <c r="F10" s="2">
-        <v>300</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" ht="13.5" customHeight="1">
-      <c r="A11" s="21" t="s">
+    </row>
+    <row r="12" spans="1:7" ht="13.5" customHeight="1">
+      <c r="A12" s="20" t="s">
         <v>187</v>
       </c>
-    </row>
-    <row r="12" spans="1:7" ht="13.5" customHeight="1">
-      <c r="A12" s="21" t="s">
+      <c r="D12" t="s">
         <v>188</v>
       </c>
-      <c r="D12" t="s">
+    </row>
+    <row r="13" spans="1:7" ht="13.5" customHeight="1">
+      <c r="A13" s="21" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="13" spans="1:7" ht="13.5" customHeight="1">
-      <c r="A13" s="22" t="s">
+      <c r="B13" s="22" t="s">
         <v>190</v>
       </c>
-      <c r="B13" s="23" t="s">
+    </row>
+    <row r="14" spans="1:7" ht="13.5" customHeight="1">
+      <c r="A14" s="22" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="13.5" customHeight="1">
-      <c r="A14" s="23" t="s">
+    <row r="15" spans="1:7" ht="13.5" customHeight="1">
+      <c r="A15" s="22" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="13.5" customHeight="1">
-      <c r="A15" s="23" t="s">
+    <row r="16" spans="1:7" ht="13.5" customHeight="1">
+      <c r="A16" s="23" t="s">
         <v>193</v>
       </c>
-    </row>
-    <row r="16" spans="1:7" ht="13.5" customHeight="1">
-      <c r="A16" s="24" t="s">
+      <c r="B16" s="24" t="s">
         <v>194</v>
       </c>
-      <c r="B16" s="25" t="s">
+    </row>
+    <row r="17" spans="1:2" ht="13.5" customHeight="1">
+      <c r="A17" s="25" t="s">
         <v>195</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" ht="13.5" customHeight="1">
-      <c r="A17" s="26" t="s">
-        <v>196</v>
       </c>
       <c r="B17">
         <v>2</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="13.5" customHeight="1">
-      <c r="A18" s="25" t="s">
-        <v>197</v>
+      <c r="A18" s="24" t="s">
+        <v>196</v>
       </c>
       <c r="B18">
         <v>3</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="13.5" customHeight="1">
-      <c r="A19" s="27" t="s">
-        <v>198</v>
+      <c r="A19" s="26" t="s">
+        <v>197</v>
       </c>
       <c r="B19">
         <v>4</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="13.5" customHeight="1">
-      <c r="A20" s="28" t="s">
-        <v>199</v>
+      <c r="A20" s="27" t="s">
+        <v>198</v>
       </c>
       <c r="B20">
         <v>4</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="13.5" customHeight="1">
-      <c r="A21" s="29" t="s">
-        <v>200</v>
+      <c r="A21" s="28" t="s">
+        <v>199</v>
       </c>
       <c r="B21">
         <v>5</v>
       </c>
     </row>
     <row r="22" spans="1:2" ht="13.5" customHeight="1">
-      <c r="A22" s="29" t="s">
-        <v>201</v>
+      <c r="A22" s="28" t="s">
+        <v>200</v>
       </c>
       <c r="B22">
         <v>5</v>
       </c>
     </row>
     <row r="23" spans="1:2" ht="13.5" customHeight="1">
-      <c r="A23" s="30" t="s">
-        <v>202</v>
+      <c r="A23" s="29" t="s">
+        <v>201</v>
       </c>
       <c r="B23">
         <v>6</v>
       </c>
     </row>
     <row r="24" spans="1:2" ht="13.5" customHeight="1">
-      <c r="A24" s="30" t="s">
-        <v>203</v>
+      <c r="A24" s="29" t="s">
+        <v>202</v>
       </c>
       <c r="B24">
         <v>6</v>
@@ -3726,20 +3802,20 @@
     </row>
     <row r="25" spans="1:2" ht="13.5" customHeight="1">
       <c r="A25" t="s">
+        <v>203</v>
+      </c>
+      <c r="B25" t="s">
         <v>204</v>
-      </c>
-      <c r="B25" t="s">
-        <v>205</v>
       </c>
     </row>
     <row r="26" spans="1:2" ht="13.5" customHeight="1">
       <c r="A26" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="27" spans="1:2" ht="13.5" customHeight="1">
       <c r="A27" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="1048573" ht="12.75" customHeight="1"/>
@@ -3761,52 +3837,52 @@
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultColWidth="10" defaultRowHeight="14.25" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="10" style="2"/>
-    <col min="2" max="2" width="30.5" style="2" customWidth="1"/>
-    <col min="3" max="3" width="10" style="2"/>
+    <col min="1" max="1" width="10" style="1"/>
+    <col min="2" max="2" width="30.5" style="1" customWidth="1"/>
+    <col min="3" max="3" width="10" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" s="1" t="s">
         <v>208</v>
       </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" s="2" t="s">
+      <c r="B2" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="C2" s="30">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="C2" s="31">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" s="2" t="s">
+      <c r="B3" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="C3" s="30">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" s="2" t="s">
         <v>212</v>
       </c>
-      <c r="C3" s="31">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" s="3" t="s">
-        <v>213</v>
-      </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="C4" s="31">
+      <c r="C4" s="30">
         <v>0.2</v>
       </c>
     </row>

--- a/assets/card_data.xlsx
+++ b/assets/card_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\cpyh\godot\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90759C4A-0E9B-4330-923D-EAAF82A6AFDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{185A7993-9D1E-4252-A20E-ACD8FC8AF42C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-21710" yWindow="-110" windowWidth="21820" windowHeight="13900" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="409" uniqueCount="279">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="408" uniqueCount="279">
   <si>
     <t>name</t>
   </si>
@@ -1380,11 +1380,11 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2471,17 +2471,17 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr defaultColWidth="10" defaultRowHeight="14.25" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="14.125" style="1" customWidth="1"/>
     <col min="2" max="3" width="10" style="1"/>
-    <col min="5" max="5" width="30.25" customWidth="1"/>
-    <col min="6" max="7" width="10" style="1"/>
-    <col min="8" max="8" width="6.625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="30.25" customWidth="1"/>
+    <col min="5" max="6" width="10" style="1"/>
+    <col min="7" max="7" width="6.625" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>30</v>
       </c>
@@ -2492,22 +2492,19 @@
         <v>34</v>
       </c>
       <c r="D1" t="s">
-        <v>36</v>
-      </c>
-      <c r="E1" t="s">
         <v>35</v>
       </c>
+      <c r="E1" s="1" t="s">
+        <v>37</v>
+      </c>
       <c r="F1" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="H1" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:8">
+    <row r="2" spans="1:7">
       <c r="A2" s="1" t="s">
         <v>60</v>
       </c>
@@ -2517,20 +2514,17 @@
       <c r="C2" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="D2">
-        <v>13</v>
-      </c>
-      <c r="F2" s="1">
+      <c r="E2" s="1">
         <v>5</v>
       </c>
+      <c r="F2" s="1" t="s">
+        <v>63</v>
+      </c>
       <c r="G2" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="H2" s="1" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="3" spans="1:8">
+    <row r="3" spans="1:7">
       <c r="A3" s="1" t="s">
         <v>65</v>
       </c>
@@ -2540,20 +2534,17 @@
       <c r="C3" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="D3">
-        <v>14</v>
-      </c>
-      <c r="F3" s="1">
+      <c r="E3" s="1">
         <v>6</v>
       </c>
+      <c r="F3" s="1" t="s">
+        <v>63</v>
+      </c>
       <c r="G3" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="H3" s="1" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="4" spans="1:8">
+    <row r="4" spans="1:7">
       <c r="A4" s="1" t="s">
         <v>69</v>
       </c>
@@ -2563,20 +2554,17 @@
       <c r="C4" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="D4">
-        <v>15</v>
-      </c>
-      <c r="F4" s="1">
+      <c r="E4" s="1">
         <v>7</v>
       </c>
+      <c r="F4" s="1" t="s">
+        <v>63</v>
+      </c>
       <c r="G4" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="H4" s="1" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="5" spans="1:8">
+    <row r="5" spans="1:7">
       <c r="A5" s="6" t="s">
         <v>16</v>
       </c>
@@ -2586,23 +2574,20 @@
       <c r="C5" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="D5">
-        <v>16</v>
-      </c>
-      <c r="E5" t="s">
+      <c r="D5" t="s">
         <v>72</v>
       </c>
-      <c r="F5" s="1">
+      <c r="E5" s="1">
         <v>8</v>
       </c>
+      <c r="F5" s="1" t="s">
+        <v>63</v>
+      </c>
       <c r="G5" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="H5" s="1" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="6" spans="1:8">
+    <row r="6" spans="1:7">
       <c r="A6" s="1" t="s">
         <v>73</v>
       </c>
@@ -2612,23 +2597,20 @@
       <c r="C6" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="D6">
-        <v>17</v>
-      </c>
-      <c r="E6" t="s">
+      <c r="D6" t="s">
         <v>75</v>
       </c>
-      <c r="F6" s="1">
+      <c r="E6" s="1">
         <v>90</v>
       </c>
+      <c r="F6" s="1" t="s">
+        <v>63</v>
+      </c>
       <c r="G6" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="H6" s="1" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="7" spans="1:8">
+    <row r="7" spans="1:7">
       <c r="A7" s="1" t="s">
         <v>76</v>
       </c>
@@ -2638,20 +2620,17 @@
       <c r="C7" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="D7">
-        <v>18</v>
-      </c>
-      <c r="F7" s="1">
+      <c r="E7" s="1">
         <v>10</v>
       </c>
+      <c r="F7" s="1" t="s">
+        <v>63</v>
+      </c>
       <c r="G7" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="H7" s="1" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="8" spans="1:8">
+    <row r="8" spans="1:7">
       <c r="A8" s="1" t="s">
         <v>78</v>
       </c>
@@ -2661,20 +2640,17 @@
       <c r="C8" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="D8">
-        <v>20</v>
-      </c>
-      <c r="F8" s="1">
+      <c r="E8" s="1">
         <v>1</v>
       </c>
+      <c r="F8" s="1" t="s">
+        <v>63</v>
+      </c>
       <c r="G8" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="H8" s="1" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="9" spans="1:8">
+    <row r="9" spans="1:7">
       <c r="A9" s="1" t="s">
         <v>80</v>
       </c>
@@ -2684,24 +2660,21 @@
       <c r="C9" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="D9">
-        <v>21</v>
-      </c>
-      <c r="E9" s="8" t="s">
+      <c r="D9" s="8" t="s">
         <v>82</v>
       </c>
-      <c r="F9" s="1">
+      <c r="E9" s="1">
         <v>150</v>
       </c>
-      <c r="G9" s="1" t="b">
+      <c r="F9" s="1" t="b">
         <f>TRUE()</f>
         <v>1</v>
       </c>
-      <c r="H9" s="1" t="s">
+      <c r="G9" s="1" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="14.25" customHeight="1">
+    <row r="10" spans="1:7" ht="14.25" customHeight="1">
       <c r="A10" s="8" t="s">
         <v>83</v>
       </c>
@@ -2711,23 +2684,20 @@
       <c r="C10" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="D10">
-        <v>22</v>
-      </c>
-      <c r="E10" s="9" t="s">
+      <c r="D10" s="9" t="s">
         <v>85</v>
       </c>
-      <c r="F10" s="1">
+      <c r="E10" s="1">
         <v>100</v>
       </c>
+      <c r="F10" s="1" t="s">
+        <v>63</v>
+      </c>
       <c r="G10" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="H10" s="1" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="14.25" customHeight="1">
+    <row r="11" spans="1:7" ht="14.25" customHeight="1">
       <c r="A11" s="8" t="s">
         <v>86</v>
       </c>
@@ -2737,23 +2707,20 @@
       <c r="C11" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="D11">
-        <v>23</v>
-      </c>
-      <c r="E11" s="9" t="s">
+      <c r="D11" s="9" t="s">
         <v>88</v>
       </c>
-      <c r="F11" s="1">
+      <c r="E11" s="1">
         <v>200</v>
       </c>
+      <c r="F11" s="1" t="s">
+        <v>63</v>
+      </c>
       <c r="G11" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="H11" s="1" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="12" spans="1:8">
+    <row r="12" spans="1:7">
       <c r="A12" s="1" t="s">
         <v>89</v>
       </c>
@@ -2763,23 +2730,20 @@
       <c r="C12" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D12">
-        <v>24</v>
-      </c>
-      <c r="E12" s="8" t="s">
+      <c r="D12" s="8" t="s">
         <v>91</v>
       </c>
-      <c r="F12" s="1">
+      <c r="E12" s="1">
         <v>60</v>
       </c>
+      <c r="F12" s="1" t="s">
+        <v>63</v>
+      </c>
       <c r="G12" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="H12" s="1" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="13" spans="1:8">
+    <row r="13" spans="1:7">
       <c r="A13" s="1" t="s">
         <v>92</v>
       </c>
@@ -2789,17 +2753,14 @@
       <c r="C13" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="D13">
-        <v>25</v>
-      </c>
-      <c r="F13" s="1">
+      <c r="E13" s="1">
         <v>120</v>
       </c>
-      <c r="G13" s="1" t="b">
+      <c r="F13" s="1" t="b">
         <f>TRUE()</f>
         <v>1</v>
       </c>
-      <c r="H13" s="1" t="s">
+      <c r="G13" s="1" t="s">
         <v>64</v>
       </c>
     </row>
@@ -2905,7 +2866,7 @@
       </c>
     </row>
     <row r="4" spans="1:10">
-      <c r="A4" s="40" t="s">
+      <c r="A4" s="39" t="s">
         <v>278</v>
       </c>
       <c r="B4" s="1" t="s">
@@ -3523,15 +3484,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="21">
-      <c r="A1" s="39" t="s">
+      <c r="A1" s="40" t="s">
         <v>152</v>
       </c>
-      <c r="B1" s="39"/>
-      <c r="C1" s="39"/>
-      <c r="D1" s="39"/>
-      <c r="E1" s="39"/>
-      <c r="F1" s="39"/>
-      <c r="G1" s="39"/>
+      <c r="B1" s="40"/>
+      <c r="C1" s="40"/>
+      <c r="D1" s="40"/>
+      <c r="E1" s="40"/>
+      <c r="F1" s="40"/>
+      <c r="G1" s="40"/>
     </row>
     <row r="2" spans="1:7" ht="18">
       <c r="A2" s="16" t="s">

--- a/assets/card_data.xlsx
+++ b/assets/card_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\cpyh\godot\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{185A7993-9D1E-4252-A20E-ACD8FC8AF42C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0E60709-C3FE-4763-8963-8933007D6B16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-21710" yWindow="-110" windowWidth="21820" windowHeight="13900" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-21710" yWindow="-110" windowWidth="21820" windowHeight="13900" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="人物" sheetId="1" r:id="rId1"/>
@@ -267,9 +267,6 @@
   </si>
   <si>
     <t>ATK+9</t>
-  </si>
-  <si>
-    <t>骨头*骨头*蛛丝</t>
   </si>
   <si>
     <t>祈愿者的盖子</t>
@@ -1062,6 +1059,10 @@
   </si>
   <si>
     <t xml:space="preserve">千人楔 </t>
+    <phoneticPr fontId="16" type="noConversion"/>
+  </si>
+  <si>
+    <t>骨头*骨头*蛛丝</t>
     <phoneticPr fontId="16" type="noConversion"/>
   </si>
 </sst>
@@ -1672,7 +1673,7 @@
         <v>3</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>4</v>
@@ -1785,10 +1786,10 @@
     </row>
     <row r="7" spans="1:21" ht="14.25" customHeight="1">
       <c r="A7" s="6" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="F7" s="6"/>
     </row>
@@ -1797,7 +1798,7 @@
         <v>26</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="9" spans="1:21" ht="14.25" customHeight="1">
@@ -1805,7 +1806,7 @@
         <v>27</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="10" spans="1:21" ht="14.25" customHeight="1">
@@ -1813,7 +1814,7 @@
         <v>28</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="11" spans="1:21" ht="14.25" customHeight="1">
@@ -1821,26 +1822,26 @@
         <v>29</v>
       </c>
       <c r="B11" s="36" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C11" s="35"/>
       <c r="G11" s="38" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="12" spans="1:21" ht="14.25" customHeight="1">
       <c r="A12" s="37" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B12" s="35"/>
       <c r="C12" s="35"/>
     </row>
     <row r="13" spans="1:21" ht="14.25" customHeight="1">
       <c r="A13" s="6" t="s">
+        <v>264</v>
+      </c>
+      <c r="B13" s="6" t="s">
         <v>265</v>
-      </c>
-      <c r="B13" s="6" t="s">
-        <v>266</v>
       </c>
     </row>
     <row r="14" spans="1:21" ht="14.25" customHeight="1">
@@ -1874,16 +1875,16 @@
         <v>30</v>
       </c>
       <c r="B1" t="s">
+        <v>212</v>
+      </c>
+      <c r="C1" t="s">
         <v>213</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>214</v>
       </c>
-      <c r="D1" t="s">
+      <c r="F1" t="s">
         <v>215</v>
-      </c>
-      <c r="F1" t="s">
-        <v>216</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>1</v>
@@ -1895,30 +1896,30 @@
         <v>3</v>
       </c>
       <c r="J1" t="s">
+        <v>216</v>
+      </c>
+      <c r="M1" s="26" t="s">
         <v>217</v>
-      </c>
-      <c r="M1" s="26" t="s">
-        <v>218</v>
       </c>
     </row>
     <row r="2" spans="1:13" ht="14.25">
       <c r="A2" s="31" t="s">
+        <v>218</v>
+      </c>
+      <c r="B2" t="s">
         <v>219</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>220</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>221</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>222</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>223</v>
-      </c>
-      <c r="F2" t="s">
-        <v>224</v>
       </c>
       <c r="G2">
         <v>30</v>
@@ -1932,91 +1933,91 @@
     </row>
     <row r="3" spans="1:13" ht="14.25">
       <c r="A3" s="32" t="s">
+        <v>224</v>
+      </c>
+      <c r="B3" t="s">
         <v>225</v>
       </c>
-      <c r="B3" t="s">
+      <c r="D3" t="s">
         <v>226</v>
-      </c>
-      <c r="D3" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="4" spans="1:13" ht="14.25">
       <c r="A4" s="10" t="s">
+        <v>227</v>
+      </c>
+      <c r="B4" t="s">
         <v>228</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
         <v>229</v>
       </c>
-      <c r="C4" t="s">
+      <c r="F4" t="s">
         <v>230</v>
       </c>
-      <c r="F4" t="s">
+      <c r="J4" t="s">
         <v>231</v>
-      </c>
-      <c r="J4" t="s">
-        <v>232</v>
       </c>
     </row>
     <row r="5" spans="1:13" ht="14.25">
       <c r="A5" s="33" t="s">
+        <v>232</v>
+      </c>
+      <c r="B5" t="s">
         <v>233</v>
-      </c>
-      <c r="B5" t="s">
-        <v>234</v>
       </c>
     </row>
     <row r="6" spans="1:13" ht="14.25">
       <c r="A6" s="33" t="s">
+        <v>234</v>
+      </c>
+      <c r="B6" t="s">
+        <v>228</v>
+      </c>
+      <c r="C6" t="s">
         <v>235</v>
       </c>
-      <c r="B6" t="s">
-        <v>229</v>
-      </c>
-      <c r="C6" t="s">
+      <c r="F6" t="s">
         <v>236</v>
-      </c>
-      <c r="F6" t="s">
-        <v>237</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="14.25">
       <c r="A7" s="34" t="s">
+        <v>237</v>
+      </c>
+      <c r="B7" t="s">
         <v>238</v>
       </c>
-      <c r="B7" t="s">
+      <c r="C7" t="s">
+        <v>229</v>
+      </c>
+      <c r="D7" t="s">
         <v>239</v>
-      </c>
-      <c r="C7" t="s">
-        <v>230</v>
-      </c>
-      <c r="D7" t="s">
-        <v>240</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="14.25">
       <c r="A8" s="33" t="s">
+        <v>240</v>
+      </c>
+      <c r="B8" t="s">
         <v>241</v>
       </c>
-      <c r="B8" t="s">
+      <c r="C8" t="s">
         <v>242</v>
       </c>
-      <c r="C8" t="s">
+      <c r="D8" t="s">
         <v>243</v>
       </c>
-      <c r="D8" t="s">
+      <c r="F8" t="s">
         <v>244</v>
-      </c>
-      <c r="F8" t="s">
-        <v>245</v>
       </c>
     </row>
     <row r="9" spans="1:13" ht="14.25">
       <c r="A9" s="10" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B9" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="D9" t="s">
         <v>48</v>
@@ -2024,43 +2025,43 @@
     </row>
     <row r="10" spans="1:13" ht="14.25">
       <c r="A10" s="32" t="s">
+        <v>246</v>
+      </c>
+      <c r="D10" t="s">
         <v>247</v>
-      </c>
-      <c r="D10" t="s">
-        <v>248</v>
       </c>
     </row>
     <row r="11" spans="1:13" ht="28.5">
       <c r="A11" s="33" t="s">
+        <v>248</v>
+      </c>
+      <c r="B11" t="s">
         <v>249</v>
       </c>
-      <c r="B11" t="s">
+      <c r="C11" t="s">
         <v>250</v>
       </c>
-      <c r="C11" t="s">
+      <c r="F11" t="s">
         <v>251</v>
-      </c>
-      <c r="F11" t="s">
-        <v>252</v>
       </c>
     </row>
     <row r="12" spans="1:13" ht="14.25">
       <c r="A12" s="33" t="s">
+        <v>252</v>
+      </c>
+      <c r="B12" t="s">
         <v>253</v>
       </c>
-      <c r="B12" t="s">
+      <c r="F12" t="s">
         <v>254</v>
-      </c>
-      <c r="F12" t="s">
-        <v>255</v>
       </c>
     </row>
     <row r="13" spans="1:13" ht="14.25">
       <c r="A13" s="10" t="s">
+        <v>255</v>
+      </c>
+      <c r="D13" t="s">
         <v>256</v>
-      </c>
-      <c r="D13" t="s">
-        <v>257</v>
       </c>
     </row>
   </sheetData>
@@ -2471,7 +2472,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr defaultColWidth="10" defaultRowHeight="14.25" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="14.125" style="1" customWidth="1"/>
@@ -2597,8 +2598,8 @@
       <c r="C6" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="D6" t="s">
-        <v>75</v>
+      <c r="D6" s="38" t="s">
+        <v>278</v>
       </c>
       <c r="E6" s="1">
         <v>90</v>
@@ -2612,13 +2613,13 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>61</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E7" s="1">
         <v>10</v>
@@ -2632,13 +2633,13 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>66</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E8" s="1">
         <v>1</v>
@@ -2652,16 +2653,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>66</v>
       </c>
       <c r="C9" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="D9" s="8" t="s">
         <v>81</v>
-      </c>
-      <c r="D9" s="8" t="s">
-        <v>82</v>
       </c>
       <c r="E9" s="1">
         <v>150</v>
@@ -2676,16 +2677,16 @@
     </row>
     <row r="10" spans="1:7" ht="14.25" customHeight="1">
       <c r="A10" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>66</v>
       </c>
       <c r="C10" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="D10" s="9" t="s">
         <v>84</v>
-      </c>
-      <c r="D10" s="9" t="s">
-        <v>85</v>
       </c>
       <c r="E10" s="1">
         <v>100</v>
@@ -2699,16 +2700,16 @@
     </row>
     <row r="11" spans="1:7" ht="14.25" customHeight="1">
       <c r="A11" s="8" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>66</v>
       </c>
       <c r="C11" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="D11" s="9" t="s">
         <v>87</v>
-      </c>
-      <c r="D11" s="9" t="s">
-        <v>88</v>
       </c>
       <c r="E11" s="1">
         <v>200</v>
@@ -2722,16 +2723,16 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>66</v>
       </c>
       <c r="C12" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="D12" s="8" t="s">
         <v>90</v>
-      </c>
-      <c r="D12" s="8" t="s">
-        <v>91</v>
       </c>
       <c r="E12" s="1">
         <v>60</v>
@@ -2745,13 +2746,13 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>61</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E13" s="1">
         <v>120</v>
@@ -2763,6 +2764,12 @@
       <c r="G13" s="1" t="s">
         <v>64</v>
       </c>
+    </row>
+    <row r="19" spans="4:4" ht="14.25" customHeight="1">
+      <c r="D19" s="38"/>
+    </row>
+    <row r="20" spans="4:4" ht="14.25" customHeight="1">
+      <c r="D20" s="38"/>
     </row>
   </sheetData>
   <phoneticPr fontId="16" type="noConversion"/>
@@ -2791,31 +2798,31 @@
         <v>30</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>94</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>95</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>38</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>12</v>
       </c>
       <c r="G1" t="s">
+        <v>96</v>
+      </c>
+      <c r="H1" t="s">
         <v>97</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>98</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>99</v>
-      </c>
-      <c r="J1" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="2" spans="1:10">
@@ -2823,7 +2830,7 @@
         <v>24</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>63</v>
@@ -2835,15 +2842,15 @@
         <v>47</v>
       </c>
       <c r="G2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>103</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>104</v>
       </c>
       <c r="D3" s="1" t="b">
         <f>TRUE()</f>
@@ -2856,21 +2863,21 @@
         <v>47</v>
       </c>
       <c r="H3" t="s">
+        <v>104</v>
+      </c>
+      <c r="I3" t="s">
         <v>105</v>
       </c>
-      <c r="I3" t="s">
+      <c r="J3" t="s">
         <v>106</v>
-      </c>
-      <c r="J3" t="s">
-        <v>107</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="39" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D4" s="1" t="b">
         <f>TRUE()</f>
@@ -2883,15 +2890,15 @@
         <v>47</v>
       </c>
       <c r="G4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="14.25" customHeight="1">
       <c r="A5" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>110</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>111</v>
       </c>
       <c r="D5" s="1" t="b">
         <f>TRUE()</f>
@@ -2904,21 +2911,21 @@
         <v>47</v>
       </c>
       <c r="H5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="I5" t="s">
+        <v>111</v>
+      </c>
+      <c r="J5" t="s">
         <v>112</v>
-      </c>
-      <c r="J5" t="s">
-        <v>113</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="14.25" customHeight="1">
       <c r="A6" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>114</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>115</v>
       </c>
       <c r="D6" s="1" t="b">
         <f>TRUE()</f>
@@ -2931,21 +2938,21 @@
         <v>47</v>
       </c>
       <c r="H6" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="I6" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="J6" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="14.25" customHeight="1">
       <c r="A7" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>117</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>118</v>
       </c>
       <c r="D7" s="1" t="b">
         <f>TRUE()</f>
@@ -2961,32 +2968,32 @@
         <v>1</v>
       </c>
       <c r="I7" t="s">
+        <v>118</v>
+      </c>
+      <c r="J7" t="s">
         <v>119</v>
-      </c>
-      <c r="J7" t="s">
-        <v>120</v>
       </c>
     </row>
     <row r="10" spans="1:10" ht="14.25" customHeight="1">
       <c r="B10" s="6" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="14.25" customHeight="1">
       <c r="B11" s="6" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="14.25" customHeight="1">
@@ -2994,13 +3001,13 @@
     </row>
     <row r="13" spans="1:10" ht="14.25" customHeight="1">
       <c r="B13" s="6" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="1048575" ht="12.75" customHeight="1"/>
@@ -3028,13 +3035,13 @@
         <v>30</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>122</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>123</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>37</v>
@@ -3042,16 +3049,16 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B2" s="1">
         <v>0</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E2" s="1">
         <v>20000</v>
@@ -3059,16 +3066,16 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B3" s="1">
         <v>1</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E3" s="1">
         <v>15000</v>
@@ -3076,16 +3083,16 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B4" s="1">
         <v>2</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E4" s="1">
         <v>10000</v>
@@ -3093,13 +3100,13 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B5" s="1">
         <v>4</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E5" s="1">
         <v>300</v>
@@ -3107,13 +3114,13 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B6" s="1">
         <v>5</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E6" s="1">
         <v>100</v>
@@ -3121,13 +3128,13 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B7" s="1">
         <v>4</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E7" s="1">
         <v>300</v>
@@ -3135,16 +3142,16 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="B8" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="C8" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="C8" s="1" t="s">
-        <v>136</v>
-      </c>
       <c r="E8" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="30" spans="7:7">
@@ -3167,35 +3174,35 @@
         <v>31</v>
       </c>
       <c r="C1" t="s">
+        <v>136</v>
+      </c>
+      <c r="D1" t="s">
         <v>137</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>138</v>
-      </c>
-      <c r="E1" t="s">
-        <v>139</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" t="s">
+        <v>139</v>
+      </c>
+      <c r="B2" t="s">
         <v>140</v>
-      </c>
-      <c r="B2" t="s">
-        <v>141</v>
       </c>
       <c r="C2">
         <v>2</v>
       </c>
       <c r="E2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C3">
         <v>10</v>
@@ -3204,40 +3211,40 @@
         <v>1</v>
       </c>
       <c r="E3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B4" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C4">
         <v>4</v>
       </c>
       <c r="E4" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B5" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C5">
         <v>1000</v>
       </c>
       <c r="E5" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
   </sheetData>
@@ -3267,12 +3274,12 @@
         <v>36</v>
       </c>
       <c r="C1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="11" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B2" s="11">
         <v>1</v>
@@ -3280,7 +3287,7 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="11" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B3" s="11">
         <v>2</v>
@@ -3352,7 +3359,7 @@
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="11" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B12" s="11">
         <v>11</v>
@@ -3408,7 +3415,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="13" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B19" s="14">
         <v>18</v>
@@ -3416,7 +3423,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="13" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B20" s="14">
         <v>20</v>
@@ -3424,7 +3431,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="13" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B21" s="14">
         <v>21</v>
@@ -3432,7 +3439,7 @@
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="15" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B22" s="14">
         <v>22</v>
@@ -3440,7 +3447,7 @@
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="15" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B23" s="14">
         <v>23</v>
@@ -3448,7 +3455,7 @@
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="13" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B24" s="14">
         <v>24</v>
@@ -3456,7 +3463,7 @@
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="13" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B25" s="14">
         <v>25</v>
@@ -3485,7 +3492,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="21">
       <c r="A1" s="40" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B1" s="40"/>
       <c r="C1" s="40"/>
@@ -3496,160 +3503,160 @@
     </row>
     <row r="2" spans="1:7" ht="18">
       <c r="A2" s="16" t="s">
+        <v>152</v>
+      </c>
+      <c r="B2" s="17" t="s">
         <v>153</v>
       </c>
-      <c r="B2" s="17" t="s">
+      <c r="C2" s="16" t="s">
         <v>154</v>
       </c>
-      <c r="C2" s="16" t="s">
+      <c r="D2" s="16" t="s">
         <v>155</v>
       </c>
-      <c r="D2" s="16" t="s">
+      <c r="E2" s="16" t="s">
         <v>156</v>
       </c>
-      <c r="E2" s="16" t="s">
+      <c r="F2" s="16" t="s">
         <v>157</v>
       </c>
-      <c r="F2" s="16" t="s">
+      <c r="G2" s="17" t="s">
         <v>158</v>
-      </c>
-      <c r="G2" s="17" t="s">
-        <v>159</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="33">
       <c r="A3" s="18" t="s">
+        <v>159</v>
+      </c>
+      <c r="B3" s="19" t="s">
         <v>160</v>
       </c>
-      <c r="B3" s="19" t="s">
+      <c r="C3" s="18" t="s">
         <v>161</v>
       </c>
-      <c r="C3" s="18" t="s">
+      <c r="D3" s="18" t="s">
         <v>162</v>
       </c>
-      <c r="D3" s="18" t="s">
+      <c r="E3" s="18" t="s">
         <v>163</v>
-      </c>
-      <c r="E3" s="18" t="s">
-        <v>164</v>
       </c>
       <c r="F3" s="18" t="b">
         <f>FALSE()</f>
         <v>0</v>
       </c>
       <c r="G3" s="19" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="33">
       <c r="A4" s="18" t="s">
+        <v>165</v>
+      </c>
+      <c r="B4" s="19" t="s">
         <v>166</v>
       </c>
-      <c r="B4" s="19" t="s">
+      <c r="C4" s="18" t="s">
+        <v>165</v>
+      </c>
+      <c r="D4" s="18" t="s">
         <v>167</v>
       </c>
-      <c r="C4" s="18" t="s">
-        <v>166</v>
-      </c>
-      <c r="D4" s="18" t="s">
+      <c r="E4" s="18" t="s">
         <v>168</v>
-      </c>
-      <c r="E4" s="18" t="s">
-        <v>169</v>
       </c>
       <c r="F4" s="18" t="b">
         <f>TRUE()</f>
         <v>1</v>
       </c>
       <c r="G4" s="19" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="16.5">
       <c r="A5" s="18" t="s">
+        <v>170</v>
+      </c>
+      <c r="B5" s="19" t="s">
         <v>171</v>
       </c>
-      <c r="B5" s="19" t="s">
+      <c r="C5" s="18" t="s">
         <v>172</v>
       </c>
-      <c r="C5" s="18" t="s">
+      <c r="D5" s="18" t="s">
         <v>173</v>
       </c>
-      <c r="D5" s="18" t="s">
+      <c r="E5" s="18" t="s">
         <v>174</v>
-      </c>
-      <c r="E5" s="18" t="s">
-        <v>175</v>
       </c>
       <c r="F5" s="18" t="b">
         <f>TRUE()</f>
         <v>1</v>
       </c>
       <c r="G5" s="19" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="16.5">
       <c r="A6" s="18" t="s">
+        <v>175</v>
+      </c>
+      <c r="B6" s="19" t="s">
         <v>176</v>
       </c>
-      <c r="B6" s="19" t="s">
+      <c r="C6" s="18" t="s">
         <v>177</v>
       </c>
-      <c r="C6" s="18" t="s">
-        <v>178</v>
-      </c>
       <c r="D6" s="18" t="s">
+        <v>167</v>
+      </c>
+      <c r="E6" s="18" t="s">
         <v>168</v>
-      </c>
-      <c r="E6" s="18" t="s">
-        <v>169</v>
       </c>
       <c r="F6" s="18" t="b">
         <f>TRUE()</f>
         <v>1</v>
       </c>
       <c r="G6" s="19" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="33">
       <c r="A7" s="18" t="s">
+        <v>178</v>
+      </c>
+      <c r="B7" s="19" t="s">
         <v>179</v>
       </c>
-      <c r="B7" s="19" t="s">
+      <c r="C7" s="18" t="s">
+        <v>161</v>
+      </c>
+      <c r="D7" s="18" t="s">
         <v>180</v>
       </c>
-      <c r="C7" s="18" t="s">
-        <v>162</v>
-      </c>
-      <c r="D7" s="18" t="s">
+      <c r="E7" s="18" t="s">
         <v>181</v>
-      </c>
-      <c r="E7" s="18" t="s">
-        <v>182</v>
       </c>
       <c r="F7" s="18" t="b">
         <f>FALSE()</f>
         <v>0</v>
       </c>
       <c r="G7" s="19" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="14.25">
       <c r="A10" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>132</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>133</v>
       </c>
       <c r="C10" s="1"/>
       <c r="D10" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="E10" s="1" t="s">
         <v>184</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>185</v>
       </c>
       <c r="F10" s="1">
         <v>300</v>
@@ -3660,46 +3667,46 @@
     </row>
     <row r="11" spans="1:7" ht="13.5" customHeight="1">
       <c r="A11" s="20" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="13.5" customHeight="1">
       <c r="A12" s="20" t="s">
+        <v>186</v>
+      </c>
+      <c r="D12" t="s">
         <v>187</v>
-      </c>
-      <c r="D12" t="s">
-        <v>188</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="13.5" customHeight="1">
       <c r="A13" s="21" t="s">
+        <v>188</v>
+      </c>
+      <c r="B13" s="22" t="s">
         <v>189</v>
-      </c>
-      <c r="B13" s="22" t="s">
-        <v>190</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="13.5" customHeight="1">
       <c r="A14" s="22" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="13.5" customHeight="1">
       <c r="A15" s="22" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="13.5" customHeight="1">
       <c r="A16" s="23" t="s">
+        <v>192</v>
+      </c>
+      <c r="B16" s="24" t="s">
         <v>193</v>
-      </c>
-      <c r="B16" s="24" t="s">
-        <v>194</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="13.5" customHeight="1">
       <c r="A17" s="25" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B17">
         <v>2</v>
@@ -3707,7 +3714,7 @@
     </row>
     <row r="18" spans="1:2" ht="13.5" customHeight="1">
       <c r="A18" s="24" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B18">
         <v>3</v>
@@ -3715,7 +3722,7 @@
     </row>
     <row r="19" spans="1:2" ht="13.5" customHeight="1">
       <c r="A19" s="26" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B19">
         <v>4</v>
@@ -3723,7 +3730,7 @@
     </row>
     <row r="20" spans="1:2" ht="13.5" customHeight="1">
       <c r="A20" s="27" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B20">
         <v>4</v>
@@ -3731,7 +3738,7 @@
     </row>
     <row r="21" spans="1:2" ht="13.5" customHeight="1">
       <c r="A21" s="28" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B21">
         <v>5</v>
@@ -3739,7 +3746,7 @@
     </row>
     <row r="22" spans="1:2" ht="13.5" customHeight="1">
       <c r="A22" s="28" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B22">
         <v>5</v>
@@ -3747,7 +3754,7 @@
     </row>
     <row r="23" spans="1:2" ht="13.5" customHeight="1">
       <c r="A23" s="29" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B23">
         <v>6</v>
@@ -3755,7 +3762,7 @@
     </row>
     <row r="24" spans="1:2" ht="13.5" customHeight="1">
       <c r="A24" s="29" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B24">
         <v>6</v>
@@ -3763,20 +3770,20 @@
     </row>
     <row r="25" spans="1:2" ht="13.5" customHeight="1">
       <c r="A25" t="s">
+        <v>202</v>
+      </c>
+      <c r="B25" t="s">
         <v>203</v>
-      </c>
-      <c r="B25" t="s">
-        <v>204</v>
       </c>
     </row>
     <row r="26" spans="1:2" ht="13.5" customHeight="1">
       <c r="A26" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="27" spans="1:2" ht="13.5" customHeight="1">
       <c r="A27" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="1048573" ht="12.75" customHeight="1"/>
@@ -3811,15 +3818,15 @@
         <v>12</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>208</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>209</v>
       </c>
       <c r="C2" s="30">
         <v>0.3</v>
@@ -3827,10 +3834,10 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>210</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>211</v>
       </c>
       <c r="C3" s="30">
         <v>0.5</v>
@@ -3838,7 +3845,7 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="2" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>47</v>

--- a/assets/card_data.xlsx
+++ b/assets/card_data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\cpyh\godot\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0E60709-C3FE-4763-8963-8933007D6B16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94BC1EA5-68CD-4FE2-AA27-A0F3BEFBD8B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-21710" yWindow="-110" windowWidth="21820" windowHeight="13900" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-21710" yWindow="-110" windowWidth="21820" windowHeight="13900" tabRatio="500" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="人物" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="408" uniqueCount="279">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="408" uniqueCount="280">
   <si>
     <t>name</t>
   </si>
@@ -1063,6 +1063,10 @@
   </si>
   <si>
     <t>骨头*骨头*蛛丝</t>
+    <phoneticPr fontId="16" type="noConversion"/>
+  </si>
+  <si>
+    <t>祈愿者的盖子</t>
     <phoneticPr fontId="16" type="noConversion"/>
   </si>
 </sst>
@@ -2612,8 +2616,8 @@
       </c>
     </row>
     <row r="7" spans="1:7">
-      <c r="A7" s="1" t="s">
-        <v>75</v>
+      <c r="A7" s="6" t="s">
+        <v>279</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>61</v>
